--- a/2026/EL MIRADOR/Marzo/Marzo - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Marzo/Marzo - EL MIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CFFAA8-24B0-4DF1-BE66-64AC3FB52BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E81A64-97FE-4B09-B46F-1F1D614D241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="404">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1093,12 +1093,6 @@
   </si>
   <si>
     <t xml:space="preserve">Patricia Mainieri </t>
-  </si>
-  <si>
-    <t>El 12A deposito 16/03 $35.500 y 361.000</t>
-  </si>
-  <si>
-    <t>Hay que sacar a Di Mito de la cadena de mails del mirador</t>
   </si>
   <si>
     <t>VTO 17/04</t>
@@ -1233,6 +1227,45 @@
 Saludos cordiales.
 Administración</t>
   </si>
+  <si>
+    <t xml:space="preserve">ANOTACION </t>
+  </si>
+  <si>
+    <t>FECHA DE LA ANOTACION:</t>
+  </si>
+  <si>
+    <t>NOMBRE:</t>
+  </si>
+  <si>
+    <t>QUEJA VIA:</t>
+  </si>
+  <si>
+    <t>WHATSAPP</t>
+  </si>
+  <si>
+    <t>MAIL</t>
+  </si>
+  <si>
+    <t>LOTE:</t>
+  </si>
+  <si>
+    <t>MOTIVO DE LA QUEJA:</t>
+  </si>
+  <si>
+    <t>6D</t>
+  </si>
+  <si>
+    <t>Anchipi</t>
+  </si>
+  <si>
+    <t>El mes pasado en la planilla ARBA el pago $39.000 y no se le restaron de la columna "saldo total" para abonar - El adjudica que lo debe abonar el propietario anterior el restante.</t>
+  </si>
+  <si>
+    <t>Local 1</t>
+  </si>
+  <si>
+    <t>$269.608 el 08/04</t>
+  </si>
 </sst>
 </file>
 
@@ -1248,7 +1281,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.000_-;\-&quot;$&quot;\ * #,##0.000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1436,8 +1469,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1525,6 +1566,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1887,14 +1940,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="346">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2207,8 +2261,6 @@
     <xf numFmtId="1" fontId="22" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2220,6 +2272,25 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2382,6 +2453,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2413,13 +2487,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2864,7 +2970,7 @@
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122" t="s">
@@ -2907,108 +3013,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="254" t="s">
+      <c r="A14" s="265" t="s">
         <v>252</v>
       </c>
-      <c r="B14" s="254"/>
-      <c r="C14" s="254"/>
-      <c r="D14" s="254"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="254"/>
-      <c r="G14" s="254"/>
-      <c r="H14" s="254"/>
-      <c r="I14" s="254"/>
-      <c r="J14" s="254"/>
+      <c r="B14" s="265"/>
+      <c r="C14" s="265"/>
+      <c r="D14" s="265"/>
+      <c r="E14" s="265"/>
+      <c r="F14" s="265"/>
+      <c r="G14" s="265"/>
+      <c r="H14" s="265"/>
+      <c r="I14" s="265"/>
+      <c r="J14" s="265"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="254"/>
-      <c r="B15" s="254"/>
-      <c r="C15" s="254"/>
-      <c r="D15" s="254"/>
-      <c r="E15" s="254"/>
-      <c r="F15" s="254"/>
-      <c r="G15" s="254"/>
-      <c r="H15" s="254"/>
-      <c r="I15" s="254"/>
-      <c r="J15" s="254"/>
+      <c r="A15" s="265"/>
+      <c r="B15" s="265"/>
+      <c r="C15" s="265"/>
+      <c r="D15" s="265"/>
+      <c r="E15" s="265"/>
+      <c r="F15" s="265"/>
+      <c r="G15" s="265"/>
+      <c r="H15" s="265"/>
+      <c r="I15" s="265"/>
+      <c r="J15" s="265"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="254"/>
-      <c r="B16" s="254"/>
-      <c r="C16" s="254"/>
-      <c r="D16" s="254"/>
-      <c r="E16" s="254"/>
-      <c r="F16" s="254"/>
-      <c r="G16" s="254"/>
-      <c r="H16" s="254"/>
-      <c r="I16" s="254"/>
-      <c r="J16" s="254"/>
+      <c r="A16" s="265"/>
+      <c r="B16" s="265"/>
+      <c r="C16" s="265"/>
+      <c r="D16" s="265"/>
+      <c r="E16" s="265"/>
+      <c r="F16" s="265"/>
+      <c r="G16" s="265"/>
+      <c r="H16" s="265"/>
+      <c r="I16" s="265"/>
+      <c r="J16" s="265"/>
     </row>
     <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="254"/>
-      <c r="B17" s="254"/>
-      <c r="C17" s="254"/>
-      <c r="D17" s="254"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
-      <c r="J17" s="254"/>
+      <c r="A17" s="265"/>
+      <c r="B17" s="265"/>
+      <c r="C17" s="265"/>
+      <c r="D17" s="265"/>
+      <c r="E17" s="265"/>
+      <c r="F17" s="265"/>
+      <c r="G17" s="265"/>
+      <c r="H17" s="265"/>
+      <c r="I17" s="265"/>
+      <c r="J17" s="265"/>
     </row>
     <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="254"/>
-      <c r="B18" s="254"/>
-      <c r="C18" s="254"/>
-      <c r="D18" s="254"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="254"/>
-      <c r="G18" s="254"/>
-      <c r="H18" s="254"/>
-      <c r="I18" s="254"/>
-      <c r="J18" s="254"/>
+      <c r="A18" s="265"/>
+      <c r="B18" s="265"/>
+      <c r="C18" s="265"/>
+      <c r="D18" s="265"/>
+      <c r="E18" s="265"/>
+      <c r="F18" s="265"/>
+      <c r="G18" s="265"/>
+      <c r="H18" s="265"/>
+      <c r="I18" s="265"/>
+      <c r="J18" s="265"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="263" t="s">
-        <v>354</v>
-      </c>
-      <c r="B20" s="263"/>
-      <c r="C20" s="263"/>
-      <c r="D20" s="263"/>
-      <c r="E20" s="263"/>
-      <c r="F20" s="263"/>
-      <c r="G20" s="263"/>
-      <c r="H20" s="263"/>
-      <c r="I20" s="263"/>
-      <c r="J20" s="263"/>
+      <c r="A20" s="274" t="s">
+        <v>352</v>
+      </c>
+      <c r="B20" s="274"/>
+      <c r="C20" s="274"/>
+      <c r="D20" s="274"/>
+      <c r="E20" s="274"/>
+      <c r="F20" s="274"/>
+      <c r="G20" s="274"/>
+      <c r="H20" s="274"/>
+      <c r="I20" s="274"/>
+      <c r="J20" s="274"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="263"/>
-      <c r="B21" s="263"/>
-      <c r="C21" s="263"/>
-      <c r="D21" s="263"/>
-      <c r="E21" s="263"/>
-      <c r="F21" s="263"/>
-      <c r="G21" s="263"/>
-      <c r="H21" s="263"/>
-      <c r="I21" s="263"/>
-      <c r="J21" s="263"/>
+      <c r="A21" s="274"/>
+      <c r="B21" s="274"/>
+      <c r="C21" s="274"/>
+      <c r="D21" s="274"/>
+      <c r="E21" s="274"/>
+      <c r="F21" s="274"/>
+      <c r="G21" s="274"/>
+      <c r="H21" s="274"/>
+      <c r="I21" s="274"/>
+      <c r="J21" s="274"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="263"/>
-      <c r="B22" s="263"/>
-      <c r="C22" s="263"/>
-      <c r="D22" s="263"/>
-      <c r="E22" s="263"/>
-      <c r="F22" s="263"/>
-      <c r="G22" s="263"/>
-      <c r="H22" s="263"/>
-      <c r="I22" s="263"/>
-      <c r="J22" s="263"/>
+      <c r="A22" s="274"/>
+      <c r="B22" s="274"/>
+      <c r="C22" s="274"/>
+      <c r="D22" s="274"/>
+      <c r="E22" s="274"/>
+      <c r="F22" s="274"/>
+      <c r="G22" s="274"/>
+      <c r="H22" s="274"/>
+      <c r="I22" s="274"/>
+      <c r="J22" s="274"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="94"/>
@@ -3041,7 +3147,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -3059,7 +3165,7 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D26" s="224">
         <v>468146</v>
@@ -3108,7 +3214,7 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D29" s="224">
         <v>489802</v>
@@ -3181,12 +3287,12 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="245" t="s">
-        <v>373</v>
+      <c r="A32" s="243" t="s">
+        <v>371</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D32" s="224">
         <v>1064500</v>
@@ -3201,11 +3307,11 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="32" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D33" s="224">
         <v>110000</v>
@@ -3337,7 +3443,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B39" s="35"/>
       <c r="C39" s="35"/>
@@ -3355,10 +3461,10 @@
         <v>240</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D40" s="224">
         <v>1609398</v>
@@ -3376,10 +3482,10 @@
         <v>240</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D41" s="224"/>
       <c r="E41" s="49"/>
@@ -3454,7 +3560,7 @@
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D44" s="44">
         <v>74221.850000000006</v>
@@ -3593,10 +3699,10 @@
       <c r="L49" s="69"/>
     </row>
     <row r="50" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="265" t="s">
-        <v>368</v>
-      </c>
-      <c r="B50" s="266"/>
+      <c r="A50" s="276" t="s">
+        <v>366</v>
+      </c>
+      <c r="B50" s="277"/>
       <c r="C50" s="6" t="s">
         <v>348</v>
       </c>
@@ -3631,10 +3737,10 @@
       <c r="L50" s="69"/>
     </row>
     <row r="51" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="265" t="s">
+      <c r="A51" s="276" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="266"/>
+      <c r="B51" s="277"/>
       <c r="C51" s="6" t="s">
         <v>348</v>
       </c>
@@ -3735,9 +3841,9 @@
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="182" t="s">
-        <v>365</v>
-      </c>
-      <c r="D54" s="252">
+        <v>363</v>
+      </c>
+      <c r="D54" s="250">
         <v>1095070.23</v>
       </c>
       <c r="E54" s="68">
@@ -3781,9 +3887,9 @@
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="182" t="s">
-        <v>359</v>
-      </c>
-      <c r="D55" s="252">
+        <v>357</v>
+      </c>
+      <c r="D55" s="250">
         <v>4513949.7699999996</v>
       </c>
       <c r="E55" s="68">
@@ -3861,11 +3967,11 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="182" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D57" s="44">
         <v>359504.14</v>
@@ -3891,12 +3997,12 @@
       <c r="N57" s="84"/>
     </row>
     <row r="58" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="261" t="s">
-        <v>366</v>
-      </c>
-      <c r="B58" s="267"/>
+      <c r="A58" s="272" t="s">
+        <v>364</v>
+      </c>
+      <c r="B58" s="278"/>
       <c r="C58" s="35" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D58" s="44">
         <v>40000</v>
@@ -3933,7 +4039,7 @@
       </c>
       <c r="B59" s="35"/>
       <c r="C59" s="182" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D59" s="44">
         <v>897585.76</v>
@@ -3985,7 +4091,7 @@
       </c>
       <c r="B60" s="35"/>
       <c r="C60" s="182" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D60" s="44">
         <v>6047.81</v>
@@ -4022,7 +4128,7 @@
       </c>
       <c r="B61" s="141"/>
       <c r="C61" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D61" s="44">
         <v>100000</v>
@@ -4143,11 +4249,11 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="45" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B66" s="192"/>
       <c r="C66" s="35" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D66" s="44">
         <v>200000</v>
@@ -4165,11 +4271,11 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="45" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B67" s="192"/>
       <c r="C67" s="35" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D67" s="44">
         <v>60000</v>
@@ -4201,12 +4307,12 @@
       <c r="L67" s="69"/>
     </row>
     <row r="68" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="265" t="s">
-        <v>360</v>
-      </c>
-      <c r="B68" s="266"/>
+      <c r="A68" s="276" t="s">
+        <v>358</v>
+      </c>
+      <c r="B68" s="277"/>
       <c r="C68" s="137" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D68" s="44">
         <v>498900</v>
@@ -4238,12 +4344,12 @@
       <c r="L68" s="69"/>
     </row>
     <row r="69" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="265" t="s">
-        <v>358</v>
-      </c>
-      <c r="B69" s="266"/>
+      <c r="A69" s="276" t="s">
+        <v>356</v>
+      </c>
+      <c r="B69" s="277"/>
       <c r="C69" s="137" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D69" s="44">
         <v>46200</v>
@@ -4275,12 +4381,12 @@
       <c r="L69" s="69"/>
     </row>
     <row r="70" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="265" t="s">
-        <v>362</v>
-      </c>
-      <c r="B70" s="266"/>
+      <c r="A70" s="276" t="s">
+        <v>360</v>
+      </c>
+      <c r="B70" s="277"/>
       <c r="C70" s="137" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D70" s="44">
         <v>191400</v>
@@ -4405,7 +4511,7 @@
         <v>37</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D75" s="44">
         <v>0</v>
@@ -4435,12 +4541,12 @@
         <v>0</v>
       </c>
       <c r="L75" s="69" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="32" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -4780,8 +4886,8 @@
       <c r="I87" s="43"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="246"/>
-      <c r="C88" s="244"/>
+      <c r="A88" s="244"/>
+      <c r="C88" s="242"/>
       <c r="D88" s="85"/>
       <c r="E88" s="43"/>
       <c r="F88" s="43"/>
@@ -4830,12 +4936,12 @@
       <c r="I92" s="60"/>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A93" s="259" t="s">
+      <c r="A93" s="270" t="s">
         <v>34</v>
       </c>
-      <c r="B93" s="260"/>
-      <c r="C93" s="260"/>
-      <c r="D93" s="260"/>
+      <c r="B93" s="271"/>
+      <c r="C93" s="271"/>
+      <c r="D93" s="271"/>
       <c r="E93" s="80" t="s">
         <v>11</v>
       </c>
@@ -4856,8 +4962,8 @@
       </c>
     </row>
     <row r="94" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="261"/>
-      <c r="B94" s="262"/>
+      <c r="A94" s="272"/>
+      <c r="B94" s="273"/>
       <c r="C94" s="82"/>
       <c r="D94" s="44"/>
       <c r="E94" s="68">
@@ -4871,8 +4977,8 @@
       <c r="J94" s="58"/>
     </row>
     <row r="95" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="261"/>
-      <c r="B95" s="262"/>
+      <c r="A95" s="272"/>
+      <c r="B95" s="273"/>
       <c r="C95" s="82"/>
       <c r="D95" s="44"/>
       <c r="E95" s="68"/>
@@ -4883,11 +4989,11 @@
       <c r="J95" s="58"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A96" s="256" t="s">
+      <c r="A96" s="267" t="s">
         <v>17</v>
       </c>
-      <c r="B96" s="257"/>
-      <c r="C96" s="258"/>
+      <c r="B96" s="268"/>
+      <c r="C96" s="269"/>
       <c r="D96" s="79">
         <f>SUM(D94:D95)</f>
         <v>0</v>
@@ -4937,92 +5043,92 @@
         <f>D85-D83</f>
         <v>12414431.279999999</v>
       </c>
-      <c r="D100" s="264" t="s">
+      <c r="D100" s="275" t="s">
         <v>293</v>
       </c>
-      <c r="E100" s="264"/>
-      <c r="F100" s="264"/>
-      <c r="G100" s="264"/>
-      <c r="H100" s="264"/>
-      <c r="I100" s="264"/>
+      <c r="E100" s="275"/>
+      <c r="F100" s="275"/>
+      <c r="G100" s="275"/>
+      <c r="H100" s="275"/>
+      <c r="I100" s="275"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D101" s="264"/>
-      <c r="E101" s="264"/>
-      <c r="F101" s="264"/>
-      <c r="G101" s="264"/>
-      <c r="H101" s="264"/>
-      <c r="I101" s="264"/>
+      <c r="D101" s="275"/>
+      <c r="E101" s="275"/>
+      <c r="F101" s="275"/>
+      <c r="G101" s="275"/>
+      <c r="H101" s="275"/>
+      <c r="I101" s="275"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="253" t="s">
+      <c r="A102" s="264" t="s">
         <v>349</v>
       </c>
-      <c r="B102" s="253"/>
-      <c r="D102" s="264"/>
-      <c r="E102" s="264"/>
-      <c r="F102" s="264"/>
-      <c r="G102" s="264"/>
-      <c r="H102" s="264"/>
-      <c r="I102" s="264"/>
+      <c r="B102" s="264"/>
+      <c r="D102" s="275"/>
+      <c r="E102" s="275"/>
+      <c r="F102" s="275"/>
+      <c r="G102" s="275"/>
+      <c r="H102" s="275"/>
+      <c r="I102" s="275"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="253"/>
-      <c r="B103" s="253"/>
-      <c r="D103" s="264"/>
-      <c r="E103" s="264"/>
-      <c r="F103" s="264"/>
-      <c r="G103" s="264"/>
-      <c r="H103" s="264"/>
-      <c r="I103" s="264"/>
+      <c r="A103" s="264"/>
+      <c r="B103" s="264"/>
+      <c r="D103" s="275"/>
+      <c r="E103" s="275"/>
+      <c r="F103" s="275"/>
+      <c r="G103" s="275"/>
+      <c r="H103" s="275"/>
+      <c r="I103" s="275"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="253"/>
-      <c r="B104" s="253"/>
-      <c r="D104" s="264"/>
-      <c r="E104" s="264"/>
-      <c r="F104" s="264"/>
-      <c r="G104" s="264"/>
-      <c r="H104" s="264"/>
-      <c r="I104" s="264"/>
+      <c r="A104" s="264"/>
+      <c r="B104" s="264"/>
+      <c r="D104" s="275"/>
+      <c r="E104" s="275"/>
+      <c r="F104" s="275"/>
+      <c r="G104" s="275"/>
+      <c r="H104" s="275"/>
+      <c r="I104" s="275"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="253"/>
-      <c r="B105" s="253"/>
-      <c r="D105" s="264"/>
-      <c r="E105" s="264"/>
-      <c r="F105" s="264"/>
-      <c r="G105" s="264"/>
-      <c r="H105" s="264"/>
-      <c r="I105" s="264"/>
+      <c r="A105" s="264"/>
+      <c r="B105" s="264"/>
+      <c r="D105" s="275"/>
+      <c r="E105" s="275"/>
+      <c r="F105" s="275"/>
+      <c r="G105" s="275"/>
+      <c r="H105" s="275"/>
+      <c r="I105" s="275"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="253"/>
-      <c r="B106" s="253"/>
-      <c r="D106" s="264"/>
-      <c r="E106" s="264"/>
-      <c r="F106" s="264"/>
-      <c r="G106" s="264"/>
-      <c r="H106" s="264"/>
-      <c r="I106" s="264"/>
+      <c r="A106" s="264"/>
+      <c r="B106" s="264"/>
+      <c r="D106" s="275"/>
+      <c r="E106" s="275"/>
+      <c r="F106" s="275"/>
+      <c r="G106" s="275"/>
+      <c r="H106" s="275"/>
+      <c r="I106" s="275"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="253"/>
-      <c r="B107" s="253"/>
-      <c r="D107" s="264"/>
-      <c r="E107" s="264"/>
-      <c r="F107" s="264"/>
-      <c r="G107" s="264"/>
-      <c r="H107" s="264"/>
-      <c r="I107" s="264"/>
+      <c r="A107" s="264"/>
+      <c r="B107" s="264"/>
+      <c r="D107" s="275"/>
+      <c r="E107" s="275"/>
+      <c r="F107" s="275"/>
+      <c r="G107" s="275"/>
+      <c r="H107" s="275"/>
+      <c r="I107" s="275"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D108" s="264"/>
-      <c r="E108" s="264"/>
-      <c r="F108" s="264"/>
-      <c r="G108" s="264"/>
-      <c r="H108" s="264"/>
-      <c r="I108" s="264"/>
+      <c r="D108" s="275"/>
+      <c r="E108" s="275"/>
+      <c r="F108" s="275"/>
+      <c r="G108" s="275"/>
+      <c r="H108" s="275"/>
+      <c r="I108" s="275"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="16" t="s">
@@ -5030,12 +5136,12 @@
       </c>
       <c r="B109" s="17"/>
       <c r="C109" s="18"/>
-      <c r="D109" s="264"/>
-      <c r="E109" s="264"/>
-      <c r="F109" s="264"/>
-      <c r="G109" s="264"/>
-      <c r="H109" s="264"/>
-      <c r="I109" s="264"/>
+      <c r="D109" s="275"/>
+      <c r="E109" s="275"/>
+      <c r="F109" s="275"/>
+      <c r="G109" s="275"/>
+      <c r="H109" s="275"/>
+      <c r="I109" s="275"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="19" t="s">
@@ -5045,12 +5151,12 @@
         <v>1499395.7189351022</v>
       </c>
       <c r="C110" s="20"/>
-      <c r="D110" s="264"/>
-      <c r="E110" s="264"/>
-      <c r="F110" s="264"/>
-      <c r="G110" s="264"/>
-      <c r="H110" s="264"/>
-      <c r="I110" s="264"/>
+      <c r="D110" s="275"/>
+      <c r="E110" s="275"/>
+      <c r="F110" s="275"/>
+      <c r="G110" s="275"/>
+      <c r="H110" s="275"/>
+      <c r="I110" s="275"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="21" t="s">
@@ -5063,28 +5169,28 @@
       <c r="C111" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D111" s="264"/>
-      <c r="E111" s="264"/>
-      <c r="F111" s="264"/>
-      <c r="G111" s="264"/>
-      <c r="H111" s="264"/>
-      <c r="I111" s="264"/>
+      <c r="D111" s="275"/>
+      <c r="E111" s="275"/>
+      <c r="F111" s="275"/>
+      <c r="G111" s="275"/>
+      <c r="H111" s="275"/>
+      <c r="I111" s="275"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="21" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B112" s="30">
         <f>ARBA!L82</f>
         <v>7428990.9099999992</v>
       </c>
       <c r="C112" s="20"/>
-      <c r="D112" s="264"/>
-      <c r="E112" s="264"/>
-      <c r="F112" s="264"/>
-      <c r="G112" s="264"/>
-      <c r="H112" s="264"/>
-      <c r="I112" s="264"/>
+      <c r="D112" s="275"/>
+      <c r="E112" s="275"/>
+      <c r="F112" s="275"/>
+      <c r="G112" s="275"/>
+      <c r="H112" s="275"/>
+      <c r="I112" s="275"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="21" t="s">
@@ -5095,12 +5201,12 @@
         <v>-12414431.279999999</v>
       </c>
       <c r="C113" s="18"/>
-      <c r="D113" s="264"/>
-      <c r="E113" s="264"/>
-      <c r="F113" s="264"/>
-      <c r="G113" s="264"/>
-      <c r="H113" s="264"/>
-      <c r="I113" s="264"/>
+      <c r="D113" s="275"/>
+      <c r="E113" s="275"/>
+      <c r="F113" s="275"/>
+      <c r="G113" s="275"/>
+      <c r="H113" s="275"/>
+      <c r="I113" s="275"/>
       <c r="K113" s="44"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
@@ -5112,12 +5218,12 @@
         <v>0</v>
       </c>
       <c r="C114" s="18"/>
-      <c r="D114" s="264"/>
-      <c r="E114" s="264"/>
-      <c r="F114" s="264"/>
-      <c r="G114" s="264"/>
-      <c r="H114" s="264"/>
-      <c r="I114" s="264"/>
+      <c r="D114" s="275"/>
+      <c r="E114" s="275"/>
+      <c r="F114" s="275"/>
+      <c r="G114" s="275"/>
+      <c r="H114" s="275"/>
+      <c r="I114" s="275"/>
       <c r="K114" s="52"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
@@ -5129,12 +5235,12 @@
         <v>818000</v>
       </c>
       <c r="C115" s="18"/>
-      <c r="D115" s="264"/>
-      <c r="E115" s="264"/>
-      <c r="F115" s="264"/>
-      <c r="G115" s="264"/>
-      <c r="H115" s="264"/>
-      <c r="I115" s="264"/>
+      <c r="D115" s="275"/>
+      <c r="E115" s="275"/>
+      <c r="F115" s="275"/>
+      <c r="G115" s="275"/>
+      <c r="H115" s="275"/>
+      <c r="I115" s="275"/>
       <c r="K115" s="52"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
@@ -5146,12 +5252,12 @@
         <v>0</v>
       </c>
       <c r="C116" s="22"/>
-      <c r="D116" s="264"/>
-      <c r="E116" s="264"/>
-      <c r="F116" s="264"/>
-      <c r="G116" s="264"/>
-      <c r="H116" s="264"/>
-      <c r="I116" s="264"/>
+      <c r="D116" s="275"/>
+      <c r="E116" s="275"/>
+      <c r="F116" s="275"/>
+      <c r="G116" s="275"/>
+      <c r="H116" s="275"/>
+      <c r="I116" s="275"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="21" t="s">
@@ -5162,28 +5268,28 @@
         <v>0</v>
       </c>
       <c r="C117" s="22"/>
-      <c r="D117" s="264"/>
-      <c r="E117" s="264"/>
-      <c r="F117" s="264"/>
-      <c r="G117" s="264"/>
-      <c r="H117" s="264"/>
-      <c r="I117" s="264"/>
+      <c r="D117" s="275"/>
+      <c r="E117" s="275"/>
+      <c r="F117" s="275"/>
+      <c r="G117" s="275"/>
+      <c r="H117" s="275"/>
+      <c r="I117" s="275"/>
     </row>
     <row r="118" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="248" t="s">
-        <v>387</v>
+      <c r="A118" s="246" t="s">
+        <v>385</v>
       </c>
       <c r="B118" s="168">
         <f>-141730-163247</f>
         <v>-304977</v>
       </c>
       <c r="C118" s="22"/>
-      <c r="D118" s="264"/>
-      <c r="E118" s="264"/>
-      <c r="F118" s="264"/>
-      <c r="G118" s="264"/>
-      <c r="H118" s="264"/>
-      <c r="I118" s="264"/>
+      <c r="D118" s="275"/>
+      <c r="E118" s="275"/>
+      <c r="F118" s="275"/>
+      <c r="G118" s="275"/>
+      <c r="H118" s="275"/>
+      <c r="I118" s="275"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="19" t="s">
@@ -5194,22 +5300,22 @@
         <v>12236086.148935104</v>
       </c>
       <c r="C119" s="70"/>
-      <c r="D119" s="264"/>
-      <c r="E119" s="264"/>
-      <c r="F119" s="264"/>
-      <c r="G119" s="264"/>
-      <c r="H119" s="264"/>
-      <c r="I119" s="264"/>
+      <c r="D119" s="275"/>
+      <c r="E119" s="275"/>
+      <c r="F119" s="275"/>
+      <c r="G119" s="275"/>
+      <c r="H119" s="275"/>
+      <c r="I119" s="275"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="22"/>
       <c r="C120" s="18"/>
-      <c r="D120" s="264"/>
-      <c r="E120" s="264"/>
-      <c r="F120" s="264"/>
-      <c r="G120" s="264"/>
-      <c r="H120" s="264"/>
-      <c r="I120" s="264"/>
+      <c r="D120" s="275"/>
+      <c r="E120" s="275"/>
+      <c r="F120" s="275"/>
+      <c r="G120" s="275"/>
+      <c r="H120" s="275"/>
+      <c r="I120" s="275"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="16" t="s">
@@ -5217,16 +5323,16 @@
       </c>
       <c r="B121" s="8"/>
       <c r="C121" s="18"/>
-      <c r="D121" s="264"/>
-      <c r="E121" s="264"/>
-      <c r="F121" s="264"/>
-      <c r="G121" s="264"/>
-      <c r="H121" s="264"/>
-      <c r="I121" s="264"/>
+      <c r="D121" s="275"/>
+      <c r="E121" s="275"/>
+      <c r="F121" s="275"/>
+      <c r="G121" s="275"/>
+      <c r="H121" s="275"/>
+      <c r="I121" s="275"/>
     </row>
     <row r="122" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="19" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B122" s="30">
         <v>673000</v>
@@ -5236,7 +5342,7 @@
     </row>
     <row r="123" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="19" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B123" s="30">
         <v>145000</v>
@@ -5339,50 +5445,50 @@
       <c r="R135" s="9"/>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B138" s="255"/>
-      <c r="C138" s="255"/>
-      <c r="D138" s="255"/>
-      <c r="E138" s="255"/>
+      <c r="B138" s="266"/>
+      <c r="C138" s="266"/>
+      <c r="D138" s="266"/>
+      <c r="E138" s="266"/>
       <c r="F138" s="90"/>
       <c r="G138" s="90"/>
       <c r="H138" s="90"/>
       <c r="I138" s="90"/>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B139" s="255"/>
-      <c r="C139" s="255"/>
-      <c r="D139" s="255"/>
-      <c r="E139" s="255"/>
+      <c r="B139" s="266"/>
+      <c r="C139" s="266"/>
+      <c r="D139" s="266"/>
+      <c r="E139" s="266"/>
       <c r="F139" s="90"/>
       <c r="G139" s="90"/>
       <c r="H139" s="90"/>
       <c r="I139" s="90"/>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B140" s="255"/>
-      <c r="C140" s="255"/>
-      <c r="D140" s="255"/>
-      <c r="E140" s="255"/>
+      <c r="B140" s="266"/>
+      <c r="C140" s="266"/>
+      <c r="D140" s="266"/>
+      <c r="E140" s="266"/>
       <c r="F140" s="90"/>
       <c r="G140" s="90"/>
       <c r="H140" s="90"/>
       <c r="I140" s="90"/>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B141" s="255"/>
-      <c r="C141" s="255"/>
-      <c r="D141" s="255"/>
-      <c r="E141" s="255"/>
+      <c r="B141" s="266"/>
+      <c r="C141" s="266"/>
+      <c r="D141" s="266"/>
+      <c r="E141" s="266"/>
       <c r="F141" s="90"/>
       <c r="G141" s="90"/>
       <c r="H141" s="90"/>
       <c r="I141" s="90"/>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B142" s="255"/>
-      <c r="C142" s="255"/>
-      <c r="D142" s="255"/>
-      <c r="E142" s="255"/>
+      <c r="B142" s="266"/>
+      <c r="C142" s="266"/>
+      <c r="D142" s="266"/>
+      <c r="E142" s="266"/>
       <c r="F142" s="90"/>
       <c r="G142" s="90"/>
       <c r="H142" s="90"/>
@@ -5439,13 +5545,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="312" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="302"/>
-      <c r="C1" s="302"/>
-      <c r="D1" s="302"/>
-      <c r="E1" s="302"/>
+      <c r="B1" s="313"/>
+      <c r="C1" s="313"/>
+      <c r="D1" s="313"/>
+      <c r="E1" s="313"/>
       <c r="F1" s="158" t="s">
         <v>285</v>
       </c>
@@ -5457,20 +5563,20 @@
       <c r="L1" s="189" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="280">
+      <c r="M1" s="291">
         <f>RESUMEN!D85-RESUMEN!D83</f>
         <v>12414431.279999999</v>
       </c>
-      <c r="N1" s="281"/>
+      <c r="N1" s="292"/>
       <c r="O1" s="159"/>
       <c r="P1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="303"/>
-      <c r="B2" s="304"/>
-      <c r="C2" s="304"/>
-      <c r="D2" s="304"/>
-      <c r="E2" s="304"/>
+      <c r="A2" s="314"/>
+      <c r="B2" s="315"/>
+      <c r="C2" s="315"/>
+      <c r="D2" s="315"/>
+      <c r="E2" s="315"/>
       <c r="F2" s="7" t="s">
         <v>284</v>
       </c>
@@ -5490,11 +5596,11 @@
       <c r="P2" s="59"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="303"/>
-      <c r="B3" s="304"/>
-      <c r="C3" s="304"/>
-      <c r="D3" s="304"/>
-      <c r="E3" s="304"/>
+      <c r="A3" s="314"/>
+      <c r="B3" s="315"/>
+      <c r="C3" s="315"/>
+      <c r="D3" s="315"/>
+      <c r="E3" s="315"/>
       <c r="F3" s="7" t="s">
         <v>286</v>
       </c>
@@ -5510,11 +5616,11 @@
       <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="305"/>
-      <c r="B4" s="306"/>
-      <c r="C4" s="306"/>
-      <c r="D4" s="306"/>
-      <c r="E4" s="306"/>
+      <c r="A4" s="316"/>
+      <c r="B4" s="317"/>
+      <c r="C4" s="317"/>
+      <c r="D4" s="317"/>
+      <c r="E4" s="317"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
       <c r="H4" s="163"/>
@@ -5530,95 +5636,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="286" t="s">
+      <c r="C5" s="297" t="s">
         <v>300</v>
       </c>
-      <c r="D5" s="287"/>
-      <c r="E5" s="287"/>
-      <c r="F5" s="287"/>
-      <c r="G5" s="287"/>
-      <c r="H5" s="287"/>
-      <c r="I5" s="287"/>
-      <c r="J5" s="287"/>
-      <c r="K5" s="287"/>
-      <c r="L5" s="287"/>
-      <c r="M5" s="287"/>
-      <c r="N5" s="287"/>
-      <c r="O5" s="288"/>
+      <c r="D5" s="298"/>
+      <c r="E5" s="298"/>
+      <c r="F5" s="298"/>
+      <c r="G5" s="298"/>
+      <c r="H5" s="298"/>
+      <c r="I5" s="298"/>
+      <c r="J5" s="298"/>
+      <c r="K5" s="298"/>
+      <c r="L5" s="298"/>
+      <c r="M5" s="298"/>
+      <c r="N5" s="298"/>
+      <c r="O5" s="299"/>
       <c r="P5" s="15"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="289"/>
-      <c r="D6" s="290"/>
-      <c r="E6" s="290"/>
-      <c r="F6" s="290"/>
-      <c r="G6" s="290"/>
-      <c r="H6" s="290"/>
-      <c r="I6" s="290"/>
-      <c r="J6" s="290"/>
-      <c r="K6" s="290"/>
-      <c r="L6" s="290"/>
-      <c r="M6" s="290"/>
-      <c r="N6" s="290"/>
-      <c r="O6" s="291"/>
+      <c r="C6" s="300"/>
+      <c r="D6" s="301"/>
+      <c r="E6" s="301"/>
+      <c r="F6" s="301"/>
+      <c r="G6" s="301"/>
+      <c r="H6" s="301"/>
+      <c r="I6" s="301"/>
+      <c r="J6" s="301"/>
+      <c r="K6" s="301"/>
+      <c r="L6" s="301"/>
+      <c r="M6" s="301"/>
+      <c r="N6" s="301"/>
+      <c r="O6" s="302"/>
       <c r="P6" s="15"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="289"/>
-      <c r="D7" s="290"/>
-      <c r="E7" s="290"/>
-      <c r="F7" s="290"/>
-      <c r="G7" s="290"/>
-      <c r="H7" s="290"/>
-      <c r="I7" s="290"/>
-      <c r="J7" s="290"/>
-      <c r="K7" s="290"/>
-      <c r="L7" s="290"/>
-      <c r="M7" s="290"/>
-      <c r="N7" s="290"/>
-      <c r="O7" s="291"/>
+      <c r="C7" s="300"/>
+      <c r="D7" s="301"/>
+      <c r="E7" s="301"/>
+      <c r="F7" s="301"/>
+      <c r="G7" s="301"/>
+      <c r="H7" s="301"/>
+      <c r="I7" s="301"/>
+      <c r="J7" s="301"/>
+      <c r="K7" s="301"/>
+      <c r="L7" s="301"/>
+      <c r="M7" s="301"/>
+      <c r="N7" s="301"/>
+      <c r="O7" s="302"/>
       <c r="P7" s="15"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="292"/>
-      <c r="D8" s="293"/>
-      <c r="E8" s="293"/>
-      <c r="F8" s="293"/>
-      <c r="G8" s="293"/>
-      <c r="H8" s="293"/>
-      <c r="I8" s="293"/>
-      <c r="J8" s="293"/>
-      <c r="K8" s="293"/>
-      <c r="L8" s="293"/>
-      <c r="M8" s="293"/>
-      <c r="N8" s="293"/>
-      <c r="O8" s="294"/>
+      <c r="C8" s="303"/>
+      <c r="D8" s="304"/>
+      <c r="E8" s="304"/>
+      <c r="F8" s="304"/>
+      <c r="G8" s="304"/>
+      <c r="H8" s="304"/>
+      <c r="I8" s="304"/>
+      <c r="J8" s="304"/>
+      <c r="K8" s="304"/>
+      <c r="L8" s="304"/>
+      <c r="M8" s="304"/>
+      <c r="N8" s="304"/>
+      <c r="O8" s="305"/>
       <c r="Q8" s="84"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="295" t="s">
+      <c r="C9" s="306" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="296"/>
-      <c r="E9" s="296"/>
-      <c r="F9" s="296"/>
-      <c r="G9" s="296"/>
-      <c r="H9" s="296"/>
-      <c r="I9" s="296"/>
-      <c r="J9" s="296"/>
-      <c r="K9" s="296"/>
-      <c r="L9" s="296"/>
-      <c r="M9" s="296"/>
-      <c r="N9" s="296"/>
-      <c r="O9" s="297"/>
+      <c r="D9" s="307"/>
+      <c r="E9" s="307"/>
+      <c r="F9" s="307"/>
+      <c r="G9" s="307"/>
+      <c r="H9" s="307"/>
+      <c r="I9" s="307"/>
+      <c r="J9" s="307"/>
+      <c r="K9" s="307"/>
+      <c r="L9" s="307"/>
+      <c r="M9" s="307"/>
+      <c r="N9" s="307"/>
+      <c r="O9" s="308"/>
       <c r="Q9" t="s">
         <v>242</v>
       </c>
@@ -5630,19 +5736,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="298"/>
-      <c r="D10" s="299"/>
-      <c r="E10" s="299"/>
-      <c r="F10" s="299"/>
-      <c r="G10" s="299"/>
-      <c r="H10" s="299"/>
-      <c r="I10" s="299"/>
-      <c r="J10" s="299"/>
-      <c r="K10" s="299"/>
-      <c r="L10" s="299"/>
-      <c r="M10" s="299"/>
-      <c r="N10" s="299"/>
-      <c r="O10" s="300"/>
+      <c r="C10" s="309"/>
+      <c r="D10" s="310"/>
+      <c r="E10" s="310"/>
+      <c r="F10" s="310"/>
+      <c r="G10" s="310"/>
+      <c r="H10" s="310"/>
+      <c r="I10" s="310"/>
+      <c r="J10" s="310"/>
+      <c r="K10" s="310"/>
+      <c r="L10" s="310"/>
+      <c r="M10" s="310"/>
+      <c r="N10" s="310"/>
+      <c r="O10" s="311"/>
       <c r="Q10" t="s">
         <v>243</v>
       </c>
@@ -5652,49 +5758,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="271" t="s">
+      <c r="A11" s="282" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="273" t="s">
+      <c r="B11" s="284" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="282" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="275" t="s">
+      <c r="D11" s="286" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="275" t="s">
+      <c r="E11" s="286" t="s">
         <v>259</v>
       </c>
-      <c r="F11" s="271" t="s">
+      <c r="F11" s="282" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="271" t="s">
+      <c r="G11" s="282" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="271" t="s">
+      <c r="H11" s="282" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="282" t="s">
+      <c r="I11" s="293" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="268" t="s">
+      <c r="J11" s="279" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="268" t="s">
-        <v>391</v>
-      </c>
-      <c r="L11" s="268" t="s">
+      <c r="K11" s="279" t="s">
+        <v>389</v>
+      </c>
+      <c r="L11" s="279" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="284" t="s">
+      <c r="M11" s="295" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="268" t="s">
+      <c r="N11" s="279" t="s">
         <v>270</v>
       </c>
-      <c r="O11" s="268" t="s">
+      <c r="O11" s="279" t="s">
         <v>269</v>
       </c>
       <c r="Q11" t="s">
@@ -5706,21 +5812,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="272"/>
-      <c r="B12" s="274"/>
-      <c r="C12" s="272"/>
-      <c r="D12" s="276"/>
-      <c r="E12" s="276"/>
-      <c r="F12" s="272"/>
-      <c r="G12" s="272"/>
-      <c r="H12" s="272"/>
-      <c r="I12" s="283"/>
-      <c r="J12" s="269"/>
-      <c r="K12" s="269"/>
-      <c r="L12" s="269"/>
-      <c r="M12" s="285"/>
-      <c r="N12" s="269"/>
-      <c r="O12" s="269"/>
+      <c r="A12" s="283"/>
+      <c r="B12" s="285"/>
+      <c r="C12" s="283"/>
+      <c r="D12" s="287"/>
+      <c r="E12" s="287"/>
+      <c r="F12" s="283"/>
+      <c r="G12" s="283"/>
+      <c r="H12" s="283"/>
+      <c r="I12" s="294"/>
+      <c r="J12" s="280"/>
+      <c r="K12" s="280"/>
+      <c r="L12" s="280"/>
+      <c r="M12" s="296"/>
+      <c r="N12" s="280"/>
+      <c r="O12" s="280"/>
       <c r="Q12" t="s">
         <v>245</v>
       </c>
@@ -5730,19 +5836,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="272"/>
-      <c r="B13" s="274"/>
-      <c r="C13" s="272"/>
-      <c r="D13" s="276"/>
-      <c r="E13" s="276"/>
-      <c r="F13" s="272"/>
-      <c r="G13" s="272"/>
-      <c r="H13" s="272"/>
-      <c r="I13" s="283"/>
-      <c r="J13" s="269"/>
-      <c r="K13" s="270"/>
-      <c r="L13" s="270"/>
-      <c r="M13" s="285"/>
+      <c r="A13" s="283"/>
+      <c r="B13" s="285"/>
+      <c r="C13" s="283"/>
+      <c r="D13" s="287"/>
+      <c r="E13" s="287"/>
+      <c r="F13" s="283"/>
+      <c r="G13" s="283"/>
+      <c r="H13" s="283"/>
+      <c r="I13" s="294"/>
+      <c r="J13" s="280"/>
+      <c r="K13" s="281"/>
+      <c r="L13" s="281"/>
+      <c r="M13" s="296"/>
       <c r="N13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/04</v>
@@ -5760,14 +5866,14 @@
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="344" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="35" t="s">
+      <c r="B14" s="344"/>
+      <c r="C14" s="344" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="108" t="s">
+      <c r="D14" s="345" t="s">
         <v>175</v>
       </c>
       <c r="E14" s="108" t="s">
@@ -5809,10 +5915,10 @@
         <v>285784.43273672013</v>
       </c>
       <c r="P14" s="115" t="s">
-        <v>386</v>
-      </c>
-      <c r="R14" s="277"/>
-      <c r="S14" s="277"/>
+        <v>384</v>
+      </c>
+      <c r="R14" s="288"/>
+      <c r="S14" s="288"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
@@ -5859,10 +5965,10 @@
         <v>230847.99638384001</v>
       </c>
       <c r="P15" s="115" t="s">
-        <v>383</v>
-      </c>
-      <c r="R15" s="277"/>
-      <c r="S15" s="277"/>
+        <v>381</v>
+      </c>
+      <c r="R15" s="288"/>
+      <c r="S15" s="288"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -5981,7 +6087,7 @@
       <c r="G18" s="151">
         <v>553901.72915400006</v>
       </c>
-      <c r="H18" s="249">
+      <c r="H18" s="247">
         <v>93261</v>
       </c>
       <c r="I18" s="152">
@@ -6030,7 +6136,7 @@
       <c r="G19" s="184">
         <v>271092.01</v>
       </c>
-      <c r="H19" s="250">
+      <c r="H19" s="248">
         <f>G19</f>
         <v>271092.01</v>
       </c>
@@ -6195,7 +6301,7 @@
       <c r="G22" s="197">
         <v>143604.04</v>
       </c>
-      <c r="H22" s="251">
+      <c r="H22" s="249">
         <v>144000</v>
       </c>
       <c r="I22" s="198">
@@ -7422,7 +7528,7 @@
         <v>183</v>
       </c>
       <c r="E41" s="135" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F41" s="136">
         <v>8.6999999999999994E-3</v>
@@ -7892,10 +7998,10 @@
         <v>122</v>
       </c>
       <c r="B46" s="170"/>
-      <c r="C46" s="35" t="s">
+      <c r="C46" s="262" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="108" t="s">
+      <c r="D46" s="263" t="s">
         <v>307</v>
       </c>
       <c r="E46" s="135"/>
@@ -8508,7 +8614,7 @@
       <c r="G57" s="197">
         <v>536768.39</v>
       </c>
-      <c r="H57" s="251">
+      <c r="H57" s="249">
         <f>568974-H101</f>
         <v>497610.17</v>
       </c>
@@ -9815,7 +9921,7 @@
       <c r="G81" s="197">
         <v>133630.63</v>
       </c>
-      <c r="H81" s="251">
+      <c r="H81" s="249">
         <f>G81</f>
         <v>133630.63</v>
       </c>
@@ -11740,7 +11846,7 @@
         <v>183</v>
       </c>
       <c r="E118" s="195" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F118" s="230">
         <v>2.3E-3</v>
@@ -11748,7 +11854,7 @@
       <c r="G118" s="197">
         <v>35329</v>
       </c>
-      <c r="H118" s="251">
+      <c r="H118" s="249">
         <f t="shared" ref="H118:H120" si="41">G118</f>
         <v>35329</v>
       </c>
@@ -12537,34 +12643,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="279"/>
-      <c r="D135" s="279"/>
-      <c r="E135" s="279"/>
-      <c r="F135" s="279"/>
-      <c r="G135" s="279"/>
-      <c r="H135" s="279"/>
-      <c r="I135" s="279"/>
-      <c r="J135" s="279"/>
-      <c r="K135" s="279"/>
-      <c r="L135" s="279"/>
-      <c r="M135" s="279"/>
-      <c r="N135" s="279"/>
-      <c r="O135" s="279"/>
+      <c r="C135" s="290"/>
+      <c r="D135" s="290"/>
+      <c r="E135" s="290"/>
+      <c r="F135" s="290"/>
+      <c r="G135" s="290"/>
+      <c r="H135" s="290"/>
+      <c r="I135" s="290"/>
+      <c r="J135" s="290"/>
+      <c r="K135" s="290"/>
+      <c r="L135" s="290"/>
+      <c r="M135" s="290"/>
+      <c r="N135" s="290"/>
+      <c r="O135" s="290"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="279"/>
-      <c r="D136" s="279"/>
-      <c r="E136" s="279"/>
-      <c r="F136" s="279"/>
-      <c r="G136" s="279"/>
-      <c r="H136" s="279"/>
-      <c r="I136" s="279"/>
-      <c r="J136" s="279"/>
-      <c r="K136" s="279"/>
-      <c r="L136" s="279"/>
-      <c r="M136" s="279"/>
-      <c r="N136" s="279"/>
-      <c r="O136" s="279"/>
+      <c r="C136" s="290"/>
+      <c r="D136" s="290"/>
+      <c r="E136" s="290"/>
+      <c r="F136" s="290"/>
+      <c r="G136" s="290"/>
+      <c r="H136" s="290"/>
+      <c r="I136" s="290"/>
+      <c r="J136" s="290"/>
+      <c r="K136" s="290"/>
+      <c r="L136" s="290"/>
+      <c r="M136" s="290"/>
+      <c r="N136" s="290"/>
+      <c r="O136" s="290"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
@@ -12582,126 +12688,126 @@
       <c r="O137" s="77"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C138" s="253" t="s">
+      <c r="C138" s="264" t="s">
         <v>252</v>
       </c>
-      <c r="D138" s="253"/>
-      <c r="E138" s="253"/>
-      <c r="F138" s="253"/>
-      <c r="G138" s="253"/>
-      <c r="H138" s="253"/>
-      <c r="I138" s="253"/>
-      <c r="J138" s="253"/>
-      <c r="K138" s="253"/>
-      <c r="L138" s="253"/>
-      <c r="M138" s="253"/>
-      <c r="N138" s="253"/>
-      <c r="O138" s="253"/>
+      <c r="D138" s="264"/>
+      <c r="E138" s="264"/>
+      <c r="F138" s="264"/>
+      <c r="G138" s="264"/>
+      <c r="H138" s="264"/>
+      <c r="I138" s="264"/>
+      <c r="J138" s="264"/>
+      <c r="K138" s="264"/>
+      <c r="L138" s="264"/>
+      <c r="M138" s="264"/>
+      <c r="N138" s="264"/>
+      <c r="O138" s="264"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C139" s="253"/>
-      <c r="D139" s="253"/>
-      <c r="E139" s="253"/>
-      <c r="F139" s="253"/>
-      <c r="G139" s="253"/>
-      <c r="H139" s="253"/>
-      <c r="I139" s="253"/>
-      <c r="J139" s="253"/>
-      <c r="K139" s="253"/>
-      <c r="L139" s="253"/>
-      <c r="M139" s="253"/>
-      <c r="N139" s="253"/>
-      <c r="O139" s="253"/>
+      <c r="C139" s="264"/>
+      <c r="D139" s="264"/>
+      <c r="E139" s="264"/>
+      <c r="F139" s="264"/>
+      <c r="G139" s="264"/>
+      <c r="H139" s="264"/>
+      <c r="I139" s="264"/>
+      <c r="J139" s="264"/>
+      <c r="K139" s="264"/>
+      <c r="L139" s="264"/>
+      <c r="M139" s="264"/>
+      <c r="N139" s="264"/>
+      <c r="O139" s="264"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C140" s="253"/>
-      <c r="D140" s="253"/>
-      <c r="E140" s="253"/>
-      <c r="F140" s="253"/>
-      <c r="G140" s="253"/>
-      <c r="H140" s="253"/>
-      <c r="I140" s="253"/>
-      <c r="J140" s="253"/>
-      <c r="K140" s="253"/>
-      <c r="L140" s="253"/>
-      <c r="M140" s="253"/>
-      <c r="N140" s="253"/>
-      <c r="O140" s="253"/>
+      <c r="C140" s="264"/>
+      <c r="D140" s="264"/>
+      <c r="E140" s="264"/>
+      <c r="F140" s="264"/>
+      <c r="G140" s="264"/>
+      <c r="H140" s="264"/>
+      <c r="I140" s="264"/>
+      <c r="J140" s="264"/>
+      <c r="K140" s="264"/>
+      <c r="L140" s="264"/>
+      <c r="M140" s="264"/>
+      <c r="N140" s="264"/>
+      <c r="O140" s="264"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="253"/>
-      <c r="D141" s="253"/>
-      <c r="E141" s="253"/>
-      <c r="F141" s="253"/>
-      <c r="G141" s="253"/>
-      <c r="H141" s="253"/>
-      <c r="I141" s="253"/>
-      <c r="J141" s="253"/>
-      <c r="K141" s="253"/>
-      <c r="L141" s="253"/>
-      <c r="M141" s="253"/>
-      <c r="N141" s="253"/>
-      <c r="O141" s="253"/>
+      <c r="C141" s="264"/>
+      <c r="D141" s="264"/>
+      <c r="E141" s="264"/>
+      <c r="F141" s="264"/>
+      <c r="G141" s="264"/>
+      <c r="H141" s="264"/>
+      <c r="I141" s="264"/>
+      <c r="J141" s="264"/>
+      <c r="K141" s="264"/>
+      <c r="L141" s="264"/>
+      <c r="M141" s="264"/>
+      <c r="N141" s="264"/>
+      <c r="O141" s="264"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C142" s="253"/>
-      <c r="D142" s="253"/>
-      <c r="E142" s="253"/>
-      <c r="F142" s="253"/>
-      <c r="G142" s="253"/>
-      <c r="H142" s="253"/>
-      <c r="I142" s="253"/>
-      <c r="J142" s="253"/>
-      <c r="K142" s="253"/>
-      <c r="L142" s="253"/>
-      <c r="M142" s="253"/>
-      <c r="N142" s="253"/>
-      <c r="O142" s="253"/>
+      <c r="C142" s="264"/>
+      <c r="D142" s="264"/>
+      <c r="E142" s="264"/>
+      <c r="F142" s="264"/>
+      <c r="G142" s="264"/>
+      <c r="H142" s="264"/>
+      <c r="I142" s="264"/>
+      <c r="J142" s="264"/>
+      <c r="K142" s="264"/>
+      <c r="L142" s="264"/>
+      <c r="M142" s="264"/>
+      <c r="N142" s="264"/>
+      <c r="O142" s="264"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C143" s="253"/>
-      <c r="D143" s="253"/>
-      <c r="E143" s="253"/>
-      <c r="F143" s="253"/>
-      <c r="G143" s="253"/>
-      <c r="H143" s="253"/>
-      <c r="I143" s="253"/>
-      <c r="J143" s="253"/>
-      <c r="K143" s="253"/>
-      <c r="L143" s="253"/>
-      <c r="M143" s="253"/>
-      <c r="N143" s="253"/>
-      <c r="O143" s="253"/>
+      <c r="C143" s="264"/>
+      <c r="D143" s="264"/>
+      <c r="E143" s="264"/>
+      <c r="F143" s="264"/>
+      <c r="G143" s="264"/>
+      <c r="H143" s="264"/>
+      <c r="I143" s="264"/>
+      <c r="J143" s="264"/>
+      <c r="K143" s="264"/>
+      <c r="L143" s="264"/>
+      <c r="M143" s="264"/>
+      <c r="N143" s="264"/>
+      <c r="O143" s="264"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C144" s="253"/>
-      <c r="D144" s="253"/>
-      <c r="E144" s="253"/>
-      <c r="F144" s="253"/>
-      <c r="G144" s="253"/>
-      <c r="H144" s="253"/>
-      <c r="I144" s="253"/>
-      <c r="J144" s="253"/>
-      <c r="K144" s="253"/>
-      <c r="L144" s="253"/>
-      <c r="M144" s="253"/>
-      <c r="N144" s="253"/>
-      <c r="O144" s="253"/>
+      <c r="C144" s="264"/>
+      <c r="D144" s="264"/>
+      <c r="E144" s="264"/>
+      <c r="F144" s="264"/>
+      <c r="G144" s="264"/>
+      <c r="H144" s="264"/>
+      <c r="I144" s="264"/>
+      <c r="J144" s="264"/>
+      <c r="K144" s="264"/>
+      <c r="L144" s="264"/>
+      <c r="M144" s="264"/>
+      <c r="N144" s="264"/>
+      <c r="O144" s="264"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C145" s="253"/>
-      <c r="D145" s="253"/>
-      <c r="E145" s="253"/>
-      <c r="F145" s="253"/>
-      <c r="G145" s="253"/>
-      <c r="H145" s="253"/>
-      <c r="I145" s="253"/>
-      <c r="J145" s="253"/>
-      <c r="K145" s="253"/>
-      <c r="L145" s="253"/>
-      <c r="M145" s="253"/>
-      <c r="N145" s="253"/>
-      <c r="O145" s="253"/>
+      <c r="C145" s="264"/>
+      <c r="D145" s="264"/>
+      <c r="E145" s="264"/>
+      <c r="F145" s="264"/>
+      <c r="G145" s="264"/>
+      <c r="H145" s="264"/>
+      <c r="I145" s="264"/>
+      <c r="J145" s="264"/>
+      <c r="K145" s="264"/>
+      <c r="L145" s="264"/>
+      <c r="M145" s="264"/>
+      <c r="N145" s="264"/>
+      <c r="O145" s="264"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="77"/>
@@ -12734,115 +12840,115 @@
       <c r="O147" s="77"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C148" s="278" t="s">
+      <c r="C148" s="289" t="s">
         <v>251</v>
       </c>
-      <c r="D148" s="278"/>
-      <c r="E148" s="278"/>
-      <c r="F148" s="278"/>
-      <c r="G148" s="278"/>
-      <c r="H148" s="278"/>
-      <c r="I148" s="278"/>
-      <c r="J148" s="278"/>
-      <c r="K148" s="278"/>
-      <c r="L148" s="278"/>
-      <c r="M148" s="278"/>
-      <c r="N148" s="278"/>
-      <c r="O148" s="278"/>
+      <c r="D148" s="289"/>
+      <c r="E148" s="289"/>
+      <c r="F148" s="289"/>
+      <c r="G148" s="289"/>
+      <c r="H148" s="289"/>
+      <c r="I148" s="289"/>
+      <c r="J148" s="289"/>
+      <c r="K148" s="289"/>
+      <c r="L148" s="289"/>
+      <c r="M148" s="289"/>
+      <c r="N148" s="289"/>
+      <c r="O148" s="289"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="278"/>
-      <c r="D149" s="278"/>
-      <c r="E149" s="278"/>
-      <c r="F149" s="278"/>
-      <c r="G149" s="278"/>
-      <c r="H149" s="278"/>
-      <c r="I149" s="278"/>
-      <c r="J149" s="278"/>
-      <c r="K149" s="278"/>
-      <c r="L149" s="278"/>
-      <c r="M149" s="278"/>
-      <c r="N149" s="278"/>
-      <c r="O149" s="278"/>
+      <c r="C149" s="289"/>
+      <c r="D149" s="289"/>
+      <c r="E149" s="289"/>
+      <c r="F149" s="289"/>
+      <c r="G149" s="289"/>
+      <c r="H149" s="289"/>
+      <c r="I149" s="289"/>
+      <c r="J149" s="289"/>
+      <c r="K149" s="289"/>
+      <c r="L149" s="289"/>
+      <c r="M149" s="289"/>
+      <c r="N149" s="289"/>
+      <c r="O149" s="289"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="278"/>
-      <c r="D150" s="278"/>
-      <c r="E150" s="278"/>
-      <c r="F150" s="278"/>
-      <c r="G150" s="278"/>
-      <c r="H150" s="278"/>
-      <c r="I150" s="278"/>
-      <c r="J150" s="278"/>
-      <c r="K150" s="278"/>
-      <c r="L150" s="278"/>
-      <c r="M150" s="278"/>
-      <c r="N150" s="278"/>
-      <c r="O150" s="278"/>
+      <c r="C150" s="289"/>
+      <c r="D150" s="289"/>
+      <c r="E150" s="289"/>
+      <c r="F150" s="289"/>
+      <c r="G150" s="289"/>
+      <c r="H150" s="289"/>
+      <c r="I150" s="289"/>
+      <c r="J150" s="289"/>
+      <c r="K150" s="289"/>
+      <c r="L150" s="289"/>
+      <c r="M150" s="289"/>
+      <c r="N150" s="289"/>
+      <c r="O150" s="289"/>
       <c r="Q150" s="84">
         <f>M1-L133</f>
         <v>467629.98223999888</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="278"/>
-      <c r="D151" s="278"/>
-      <c r="E151" s="278"/>
-      <c r="F151" s="278"/>
-      <c r="G151" s="278"/>
-      <c r="H151" s="278"/>
-      <c r="I151" s="278"/>
-      <c r="J151" s="278"/>
-      <c r="K151" s="278"/>
-      <c r="L151" s="278"/>
-      <c r="M151" s="278"/>
-      <c r="N151" s="278"/>
-      <c r="O151" s="278"/>
+      <c r="C151" s="289"/>
+      <c r="D151" s="289"/>
+      <c r="E151" s="289"/>
+      <c r="F151" s="289"/>
+      <c r="G151" s="289"/>
+      <c r="H151" s="289"/>
+      <c r="I151" s="289"/>
+      <c r="J151" s="289"/>
+      <c r="K151" s="289"/>
+      <c r="L151" s="289"/>
+      <c r="M151" s="289"/>
+      <c r="N151" s="289"/>
+      <c r="O151" s="289"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="278"/>
-      <c r="D152" s="278"/>
-      <c r="E152" s="278"/>
-      <c r="F152" s="278"/>
-      <c r="G152" s="278"/>
-      <c r="H152" s="278"/>
-      <c r="I152" s="278"/>
-      <c r="J152" s="278"/>
-      <c r="K152" s="278"/>
-      <c r="L152" s="278"/>
-      <c r="M152" s="278"/>
-      <c r="N152" s="278"/>
-      <c r="O152" s="278"/>
+      <c r="C152" s="289"/>
+      <c r="D152" s="289"/>
+      <c r="E152" s="289"/>
+      <c r="F152" s="289"/>
+      <c r="G152" s="289"/>
+      <c r="H152" s="289"/>
+      <c r="I152" s="289"/>
+      <c r="J152" s="289"/>
+      <c r="K152" s="289"/>
+      <c r="L152" s="289"/>
+      <c r="M152" s="289"/>
+      <c r="N152" s="289"/>
+      <c r="O152" s="289"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="278"/>
-      <c r="D153" s="278"/>
-      <c r="E153" s="278"/>
-      <c r="F153" s="278"/>
-      <c r="G153" s="278"/>
-      <c r="H153" s="278"/>
-      <c r="I153" s="278"/>
-      <c r="J153" s="278"/>
-      <c r="K153" s="278"/>
-      <c r="L153" s="278"/>
-      <c r="M153" s="278"/>
-      <c r="N153" s="278"/>
-      <c r="O153" s="278"/>
+      <c r="C153" s="289"/>
+      <c r="D153" s="289"/>
+      <c r="E153" s="289"/>
+      <c r="F153" s="289"/>
+      <c r="G153" s="289"/>
+      <c r="H153" s="289"/>
+      <c r="I153" s="289"/>
+      <c r="J153" s="289"/>
+      <c r="K153" s="289"/>
+      <c r="L153" s="289"/>
+      <c r="M153" s="289"/>
+      <c r="N153" s="289"/>
+      <c r="O153" s="289"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="278"/>
-      <c r="D154" s="278"/>
-      <c r="E154" s="278"/>
-      <c r="F154" s="278"/>
-      <c r="G154" s="278"/>
-      <c r="H154" s="278"/>
-      <c r="I154" s="278"/>
-      <c r="J154" s="278"/>
-      <c r="K154" s="278"/>
-      <c r="L154" s="278"/>
-      <c r="M154" s="278"/>
-      <c r="N154" s="278"/>
-      <c r="O154" s="278"/>
+      <c r="C154" s="289"/>
+      <c r="D154" s="289"/>
+      <c r="E154" s="289"/>
+      <c r="F154" s="289"/>
+      <c r="G154" s="289"/>
+      <c r="H154" s="289"/>
+      <c r="I154" s="289"/>
+      <c r="J154" s="289"/>
+      <c r="K154" s="289"/>
+      <c r="L154" s="289"/>
+      <c r="M154" s="289"/>
+      <c r="N154" s="289"/>
+      <c r="O154" s="289"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -12901,61 +13007,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="322" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="310"/>
-      <c r="C1" s="310"/>
-      <c r="D1" s="310"/>
-      <c r="E1" s="310"/>
-      <c r="F1" s="310"/>
-      <c r="G1" s="310"/>
-      <c r="H1" s="310"/>
-      <c r="I1" s="310"/>
-      <c r="J1" s="310"/>
-      <c r="K1" s="310"/>
-      <c r="L1" s="310"/>
-      <c r="M1" s="310"/>
-      <c r="N1" s="310"/>
-      <c r="O1" s="311"/>
+      <c r="B1" s="322"/>
+      <c r="C1" s="322"/>
+      <c r="D1" s="322"/>
+      <c r="E1" s="322"/>
+      <c r="F1" s="322"/>
+      <c r="G1" s="322"/>
+      <c r="H1" s="322"/>
+      <c r="I1" s="322"/>
+      <c r="J1" s="322"/>
+      <c r="K1" s="322"/>
+      <c r="L1" s="322"/>
+      <c r="M1" s="322"/>
+      <c r="N1" s="322"/>
+      <c r="O1" s="323"/>
       <c r="R1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="312"/>
-      <c r="B2" s="312"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="312"/>
-      <c r="E2" s="312"/>
-      <c r="F2" s="312"/>
-      <c r="G2" s="312"/>
-      <c r="H2" s="312"/>
-      <c r="I2" s="312"/>
-      <c r="J2" s="312"/>
-      <c r="K2" s="312"/>
-      <c r="L2" s="312"/>
-      <c r="M2" s="312"/>
-      <c r="N2" s="312"/>
-      <c r="O2" s="313"/>
+      <c r="A2" s="324"/>
+      <c r="B2" s="324"/>
+      <c r="C2" s="324"/>
+      <c r="D2" s="324"/>
+      <c r="E2" s="324"/>
+      <c r="F2" s="324"/>
+      <c r="G2" s="324"/>
+      <c r="H2" s="324"/>
+      <c r="I2" s="324"/>
+      <c r="J2" s="324"/>
+      <c r="K2" s="324"/>
+      <c r="L2" s="324"/>
+      <c r="M2" s="324"/>
+      <c r="N2" s="324"/>
+      <c r="O2" s="325"/>
       <c r="R2" s="43"/>
     </row>
     <row r="3" spans="1:27" s="240" customFormat="1" ht="299.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="307" t="s">
-        <v>392</v>
-      </c>
-      <c r="B3" s="308"/>
-      <c r="C3" s="308"/>
-      <c r="D3" s="308"/>
-      <c r="E3" s="308"/>
-      <c r="F3" s="308"/>
-      <c r="G3" s="308"/>
-      <c r="H3" s="308"/>
-      <c r="I3" s="308"/>
-      <c r="J3" s="308"/>
-      <c r="K3" s="308"/>
-      <c r="L3" s="308"/>
-      <c r="M3" s="308"/>
-      <c r="N3" s="308"/>
-      <c r="O3" s="309"/>
+      <c r="A3" s="319" t="s">
+        <v>390</v>
+      </c>
+      <c r="B3" s="320"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="320"/>
+      <c r="J3" s="320"/>
+      <c r="K3" s="320"/>
+      <c r="L3" s="320"/>
+      <c r="M3" s="320"/>
+      <c r="N3" s="320"/>
+      <c r="O3" s="321"/>
       <c r="P3" s="241"/>
       <c r="Q3" s="241"/>
       <c r="R3" s="241"/>
@@ -12970,85 +13076,85 @@
       <c r="AA3" s="241"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="271" t="s">
+      <c r="A4" s="282" t="s">
         <v>315</v>
       </c>
-      <c r="B4" s="271" t="s">
+      <c r="B4" s="282" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="282" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="271" t="s">
+      <c r="D4" s="282" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="268" t="s">
+      <c r="E4" s="279" t="s">
         <v>342</v>
       </c>
-      <c r="F4" s="268" t="s">
+      <c r="F4" s="279" t="s">
         <v>343</v>
       </c>
-      <c r="G4" s="268" t="s">
+      <c r="G4" s="279" t="s">
         <v>270</v>
       </c>
-      <c r="H4" s="268" t="s">
+      <c r="H4" s="279" t="s">
         <v>350</v>
       </c>
-      <c r="I4" s="268" t="s">
-        <v>381</v>
-      </c>
-      <c r="J4" s="314" t="s">
+      <c r="I4" s="279" t="s">
+        <v>379</v>
+      </c>
+      <c r="J4" s="326" t="s">
         <v>344</v>
       </c>
       <c r="K4" s="131"/>
-      <c r="L4" s="268" t="s">
-        <v>378</v>
-      </c>
-      <c r="M4" s="268" t="s">
-        <v>379</v>
-      </c>
-      <c r="N4" s="268" t="s">
+      <c r="L4" s="279" t="s">
+        <v>376</v>
+      </c>
+      <c r="M4" s="279" t="s">
+        <v>377</v>
+      </c>
+      <c r="N4" s="279" t="s">
         <v>345</v>
       </c>
-      <c r="O4" s="268" t="s">
+      <c r="O4" s="279" t="s">
         <v>17</v>
       </c>
       <c r="R4" s="43"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="272"/>
-      <c r="B5" s="272"/>
-      <c r="C5" s="272"/>
-      <c r="D5" s="272"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="315"/>
+      <c r="A5" s="283"/>
+      <c r="B5" s="283"/>
+      <c r="C5" s="283"/>
+      <c r="D5" s="283"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+      <c r="I5" s="280"/>
+      <c r="J5" s="327"/>
       <c r="K5" s="131"/>
-      <c r="L5" s="269"/>
-      <c r="M5" s="269"/>
-      <c r="N5" s="269"/>
-      <c r="O5" s="269"/>
+      <c r="L5" s="280"/>
+      <c r="M5" s="280"/>
+      <c r="N5" s="280"/>
+      <c r="O5" s="280"/>
       <c r="R5" s="43"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="318"/>
-      <c r="B6" s="318"/>
-      <c r="C6" s="318"/>
-      <c r="D6" s="318"/>
-      <c r="E6" s="317"/>
-      <c r="F6" s="317"/>
-      <c r="G6" s="317"/>
-      <c r="H6" s="317"/>
-      <c r="I6" s="317"/>
-      <c r="J6" s="316"/>
+      <c r="A6" s="329"/>
+      <c r="B6" s="329"/>
+      <c r="C6" s="329"/>
+      <c r="D6" s="329"/>
+      <c r="E6" s="318"/>
+      <c r="F6" s="318"/>
+      <c r="G6" s="318"/>
+      <c r="H6" s="318"/>
+      <c r="I6" s="318"/>
+      <c r="J6" s="328"/>
       <c r="K6" s="205"/>
-      <c r="L6" s="317"/>
-      <c r="M6" s="317"/>
-      <c r="N6" s="317"/>
-      <c r="O6" s="317"/>
+      <c r="L6" s="318"/>
+      <c r="M6" s="318"/>
+      <c r="N6" s="318"/>
+      <c r="O6" s="318"/>
       <c r="R6" s="43"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
@@ -13105,8 +13211,8 @@
       <c r="P7" s="115">
         <v>0.7</v>
       </c>
-      <c r="R7" s="277"/>
-      <c r="S7" s="277"/>
+      <c r="R7" s="288"/>
+      <c r="S7" s="288"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="206" t="s">
@@ -13160,8 +13266,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="277"/>
-      <c r="S8" s="277"/>
+      <c r="R8" s="288"/>
+      <c r="S8" s="288"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="206" t="s">
@@ -17625,7 +17731,7 @@
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
-      <c r="L82" s="247">
+      <c r="L82" s="245">
         <f>SUM(L7:L80)</f>
         <v>7428990.9099999992</v>
       </c>
@@ -17639,6 +17745,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
@@ -17654,8 +17762,6 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17664,21 +17770,207 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C4:C13"/>
+  <dimension ref="C2:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C4" s="242" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="243" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" s="251" t="s">
+        <v>391</v>
+      </c>
+      <c r="D3" s="252">
+        <v>1</v>
+      </c>
+      <c r="E3" s="252"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="254"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="255" t="s">
+        <v>392</v>
+      </c>
+      <c r="D4" s="256"/>
+      <c r="E4" s="257">
+        <v>0</v>
+      </c>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73" t="s">
+        <v>393</v>
+      </c>
+      <c r="H4" s="258" t="s">
+        <v>400</v>
+      </c>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="255" t="s">
+        <v>394</v>
+      </c>
+      <c r="D5" s="256" t="s">
+        <v>395</v>
+      </c>
+      <c r="E5" s="256" t="s">
+        <v>396</v>
+      </c>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73" t="s">
+        <v>397</v>
+      </c>
+      <c r="H5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I5" s="259"/>
+      <c r="J5" s="260"/>
+    </row>
+    <row r="6" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="244" t="s">
+        <v>398</v>
+      </c>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="261"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="330" t="s">
+        <v>401</v>
+      </c>
+      <c r="D7" s="331"/>
+      <c r="E7" s="331"/>
+      <c r="F7" s="331"/>
+      <c r="G7" s="331"/>
+      <c r="H7" s="331"/>
+      <c r="I7" s="331"/>
+      <c r="J7" s="332"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="333"/>
+      <c r="D8" s="334"/>
+      <c r="E8" s="334"/>
+      <c r="F8" s="334"/>
+      <c r="G8" s="334"/>
+      <c r="H8" s="334"/>
+      <c r="I8" s="334"/>
+      <c r="J8" s="335"/>
+    </row>
+    <row r="9" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="336"/>
+      <c r="D9" s="337"/>
+      <c r="E9" s="337"/>
+      <c r="F9" s="337"/>
+      <c r="G9" s="337"/>
+      <c r="H9" s="337"/>
+      <c r="I9" s="337"/>
+      <c r="J9" s="338"/>
+    </row>
+    <row r="11" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="339" t="s">
+        <v>391</v>
+      </c>
+      <c r="D12" s="340">
+        <f>D3+1</f>
+        <v>2</v>
+      </c>
+      <c r="E12" s="340"/>
+      <c r="F12" s="253"/>
+      <c r="G12" s="253"/>
+      <c r="H12" s="253"/>
+      <c r="I12" s="253"/>
+      <c r="J12" s="254"/>
+    </row>
+    <row r="13" spans="3:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="341" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="342"/>
+      <c r="E13" s="343">
+        <v>0</v>
+      </c>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73" t="s">
+        <v>393</v>
+      </c>
+      <c r="H13" s="258"/>
+      <c r="I13" s="259"/>
+      <c r="J13" s="260"/>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="341" t="s">
+        <v>394</v>
+      </c>
+      <c r="D14" s="342" t="s">
+        <v>395</v>
+      </c>
+      <c r="E14" s="342" t="s">
+        <v>396</v>
+      </c>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73" t="s">
+        <v>397</v>
+      </c>
+      <c r="H14" t="s">
+        <v>402</v>
+      </c>
+      <c r="I14" s="259"/>
+      <c r="J14" s="260"/>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="244" t="s">
+        <v>398</v>
+      </c>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="261"/>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="330" t="s">
+        <v>403</v>
+      </c>
+      <c r="D16" s="331"/>
+      <c r="E16" s="331"/>
+      <c r="F16" s="331"/>
+      <c r="G16" s="331"/>
+      <c r="H16" s="331"/>
+      <c r="I16" s="331"/>
+      <c r="J16" s="332"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="333"/>
+      <c r="D17" s="334"/>
+      <c r="E17" s="334"/>
+      <c r="F17" s="334"/>
+      <c r="G17" s="334"/>
+      <c r="H17" s="334"/>
+      <c r="I17" s="334"/>
+      <c r="J17" s="335"/>
+    </row>
+    <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="336"/>
+      <c r="D18" s="337"/>
+      <c r="E18" s="337"/>
+      <c r="F18" s="337"/>
+      <c r="G18" s="337"/>
+      <c r="H18" s="337"/>
+      <c r="I18" s="337"/>
+      <c r="J18" s="338"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C7:J9"/>
+    <mergeCell ref="C16:J18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2026/EL MIRADOR/Marzo/Marzo - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Marzo/Marzo - EL MIRADOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E81A64-97FE-4B09-B46F-1F1D614D241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D77AE9F-A9D1-4D90-802E-F202EC4F9927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="411">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1265,6 +1265,27 @@
   </si>
   <si>
     <t>$269.608 el 08/04</t>
+  </si>
+  <si>
+    <t>Local 2</t>
+  </si>
+  <si>
+    <t>$148.104 el 17/04</t>
+  </si>
+  <si>
+    <t>Deposito $300.000 y $30.000 23/04</t>
+  </si>
+  <si>
+    <t>No sabemos</t>
+  </si>
+  <si>
+    <t>Veronica(?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2E, 6E, 9E y cochera 12</t>
+  </si>
+  <si>
+    <t>Deposito $673.000 el 16/04</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1499,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1578,6 +1599,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1948,7 +1975,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="346">
+  <cellXfs count="363">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2291,6 +2318,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2336,35 +2380,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2383,6 +2406,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2453,8 +2485,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2487,6 +2528,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2516,13 +2560,13 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -3013,108 +3057,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="265" t="s">
+      <c r="A14" s="282" t="s">
         <v>252</v>
       </c>
-      <c r="B14" s="265"/>
-      <c r="C14" s="265"/>
-      <c r="D14" s="265"/>
-      <c r="E14" s="265"/>
-      <c r="F14" s="265"/>
-      <c r="G14" s="265"/>
-      <c r="H14" s="265"/>
-      <c r="I14" s="265"/>
-      <c r="J14" s="265"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="282"/>
+      <c r="D14" s="282"/>
+      <c r="E14" s="282"/>
+      <c r="F14" s="282"/>
+      <c r="G14" s="282"/>
+      <c r="H14" s="282"/>
+      <c r="I14" s="282"/>
+      <c r="J14" s="282"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="265"/>
-      <c r="B15" s="265"/>
-      <c r="C15" s="265"/>
-      <c r="D15" s="265"/>
-      <c r="E15" s="265"/>
-      <c r="F15" s="265"/>
-      <c r="G15" s="265"/>
-      <c r="H15" s="265"/>
-      <c r="I15" s="265"/>
-      <c r="J15" s="265"/>
+      <c r="A15" s="282"/>
+      <c r="B15" s="282"/>
+      <c r="C15" s="282"/>
+      <c r="D15" s="282"/>
+      <c r="E15" s="282"/>
+      <c r="F15" s="282"/>
+      <c r="G15" s="282"/>
+      <c r="H15" s="282"/>
+      <c r="I15" s="282"/>
+      <c r="J15" s="282"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="265"/>
-      <c r="B16" s="265"/>
-      <c r="C16" s="265"/>
-      <c r="D16" s="265"/>
-      <c r="E16" s="265"/>
-      <c r="F16" s="265"/>
-      <c r="G16" s="265"/>
-      <c r="H16" s="265"/>
-      <c r="I16" s="265"/>
-      <c r="J16" s="265"/>
+      <c r="A16" s="282"/>
+      <c r="B16" s="282"/>
+      <c r="C16" s="282"/>
+      <c r="D16" s="282"/>
+      <c r="E16" s="282"/>
+      <c r="F16" s="282"/>
+      <c r="G16" s="282"/>
+      <c r="H16" s="282"/>
+      <c r="I16" s="282"/>
+      <c r="J16" s="282"/>
     </row>
     <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="265"/>
-      <c r="B17" s="265"/>
-      <c r="C17" s="265"/>
-      <c r="D17" s="265"/>
-      <c r="E17" s="265"/>
-      <c r="F17" s="265"/>
-      <c r="G17" s="265"/>
-      <c r="H17" s="265"/>
-      <c r="I17" s="265"/>
-      <c r="J17" s="265"/>
+      <c r="A17" s="282"/>
+      <c r="B17" s="282"/>
+      <c r="C17" s="282"/>
+      <c r="D17" s="282"/>
+      <c r="E17" s="282"/>
+      <c r="F17" s="282"/>
+      <c r="G17" s="282"/>
+      <c r="H17" s="282"/>
+      <c r="I17" s="282"/>
+      <c r="J17" s="282"/>
     </row>
     <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="265"/>
-      <c r="B18" s="265"/>
-      <c r="C18" s="265"/>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="265"/>
-      <c r="I18" s="265"/>
-      <c r="J18" s="265"/>
+      <c r="A18" s="282"/>
+      <c r="B18" s="282"/>
+      <c r="C18" s="282"/>
+      <c r="D18" s="282"/>
+      <c r="E18" s="282"/>
+      <c r="F18" s="282"/>
+      <c r="G18" s="282"/>
+      <c r="H18" s="282"/>
+      <c r="I18" s="282"/>
+      <c r="J18" s="282"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="274" t="s">
+      <c r="A20" s="291" t="s">
         <v>352</v>
       </c>
-      <c r="B20" s="274"/>
-      <c r="C20" s="274"/>
-      <c r="D20" s="274"/>
-      <c r="E20" s="274"/>
-      <c r="F20" s="274"/>
-      <c r="G20" s="274"/>
-      <c r="H20" s="274"/>
-      <c r="I20" s="274"/>
-      <c r="J20" s="274"/>
+      <c r="B20" s="291"/>
+      <c r="C20" s="291"/>
+      <c r="D20" s="291"/>
+      <c r="E20" s="291"/>
+      <c r="F20" s="291"/>
+      <c r="G20" s="291"/>
+      <c r="H20" s="291"/>
+      <c r="I20" s="291"/>
+      <c r="J20" s="291"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="274"/>
-      <c r="B21" s="274"/>
-      <c r="C21" s="274"/>
-      <c r="D21" s="274"/>
-      <c r="E21" s="274"/>
-      <c r="F21" s="274"/>
-      <c r="G21" s="274"/>
-      <c r="H21" s="274"/>
-      <c r="I21" s="274"/>
-      <c r="J21" s="274"/>
+      <c r="A21" s="291"/>
+      <c r="B21" s="291"/>
+      <c r="C21" s="291"/>
+      <c r="D21" s="291"/>
+      <c r="E21" s="291"/>
+      <c r="F21" s="291"/>
+      <c r="G21" s="291"/>
+      <c r="H21" s="291"/>
+      <c r="I21" s="291"/>
+      <c r="J21" s="291"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="274"/>
-      <c r="B22" s="274"/>
-      <c r="C22" s="274"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="274"/>
-      <c r="F22" s="274"/>
-      <c r="G22" s="274"/>
-      <c r="H22" s="274"/>
-      <c r="I22" s="274"/>
-      <c r="J22" s="274"/>
+      <c r="A22" s="291"/>
+      <c r="B22" s="291"/>
+      <c r="C22" s="291"/>
+      <c r="D22" s="291"/>
+      <c r="E22" s="291"/>
+      <c r="F22" s="291"/>
+      <c r="G22" s="291"/>
+      <c r="H22" s="291"/>
+      <c r="I22" s="291"/>
+      <c r="J22" s="291"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="94"/>
@@ -3699,10 +3743,10 @@
       <c r="L49" s="69"/>
     </row>
     <row r="50" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="276" t="s">
+      <c r="A50" s="293" t="s">
         <v>366</v>
       </c>
-      <c r="B50" s="277"/>
+      <c r="B50" s="294"/>
       <c r="C50" s="6" t="s">
         <v>348</v>
       </c>
@@ -3737,10 +3781,10 @@
       <c r="L50" s="69"/>
     </row>
     <row r="51" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="276" t="s">
+      <c r="A51" s="293" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="277"/>
+      <c r="B51" s="294"/>
       <c r="C51" s="6" t="s">
         <v>348</v>
       </c>
@@ -3997,10 +4041,10 @@
       <c r="N57" s="84"/>
     </row>
     <row r="58" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="272" t="s">
+      <c r="A58" s="289" t="s">
         <v>364</v>
       </c>
-      <c r="B58" s="278"/>
+      <c r="B58" s="295"/>
       <c r="C58" s="35" t="s">
         <v>362</v>
       </c>
@@ -4307,10 +4351,10 @@
       <c r="L67" s="69"/>
     </row>
     <row r="68" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="276" t="s">
+      <c r="A68" s="293" t="s">
         <v>358</v>
       </c>
-      <c r="B68" s="277"/>
+      <c r="B68" s="294"/>
       <c r="C68" s="137" t="s">
         <v>359</v>
       </c>
@@ -4344,10 +4388,10 @@
       <c r="L68" s="69"/>
     </row>
     <row r="69" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="276" t="s">
+      <c r="A69" s="293" t="s">
         <v>356</v>
       </c>
-      <c r="B69" s="277"/>
+      <c r="B69" s="294"/>
       <c r="C69" s="137" t="s">
         <v>357</v>
       </c>
@@ -4381,10 +4425,10 @@
       <c r="L69" s="69"/>
     </row>
     <row r="70" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="276" t="s">
+      <c r="A70" s="293" t="s">
         <v>360</v>
       </c>
-      <c r="B70" s="277"/>
+      <c r="B70" s="294"/>
       <c r="C70" s="137" t="s">
         <v>359</v>
       </c>
@@ -4936,12 +4980,12 @@
       <c r="I92" s="60"/>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A93" s="270" t="s">
+      <c r="A93" s="287" t="s">
         <v>34</v>
       </c>
-      <c r="B93" s="271"/>
-      <c r="C93" s="271"/>
-      <c r="D93" s="271"/>
+      <c r="B93" s="288"/>
+      <c r="C93" s="288"/>
+      <c r="D93" s="288"/>
       <c r="E93" s="80" t="s">
         <v>11</v>
       </c>
@@ -4962,8 +5006,8 @@
       </c>
     </row>
     <row r="94" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="272"/>
-      <c r="B94" s="273"/>
+      <c r="A94" s="289"/>
+      <c r="B94" s="290"/>
       <c r="C94" s="82"/>
       <c r="D94" s="44"/>
       <c r="E94" s="68">
@@ -4977,8 +5021,8 @@
       <c r="J94" s="58"/>
     </row>
     <row r="95" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="272"/>
-      <c r="B95" s="273"/>
+      <c r="A95" s="289"/>
+      <c r="B95" s="290"/>
       <c r="C95" s="82"/>
       <c r="D95" s="44"/>
       <c r="E95" s="68"/>
@@ -4989,11 +5033,11 @@
       <c r="J95" s="58"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A96" s="267" t="s">
+      <c r="A96" s="284" t="s">
         <v>17</v>
       </c>
-      <c r="B96" s="268"/>
-      <c r="C96" s="269"/>
+      <c r="B96" s="285"/>
+      <c r="C96" s="286"/>
       <c r="D96" s="79">
         <f>SUM(D94:D95)</f>
         <v>0</v>
@@ -5043,92 +5087,92 @@
         <f>D85-D83</f>
         <v>12414431.279999999</v>
       </c>
-      <c r="D100" s="275" t="s">
+      <c r="D100" s="292" t="s">
         <v>293</v>
       </c>
-      <c r="E100" s="275"/>
-      <c r="F100" s="275"/>
-      <c r="G100" s="275"/>
-      <c r="H100" s="275"/>
-      <c r="I100" s="275"/>
+      <c r="E100" s="292"/>
+      <c r="F100" s="292"/>
+      <c r="G100" s="292"/>
+      <c r="H100" s="292"/>
+      <c r="I100" s="292"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D101" s="275"/>
-      <c r="E101" s="275"/>
-      <c r="F101" s="275"/>
-      <c r="G101" s="275"/>
-      <c r="H101" s="275"/>
-      <c r="I101" s="275"/>
+      <c r="D101" s="292"/>
+      <c r="E101" s="292"/>
+      <c r="F101" s="292"/>
+      <c r="G101" s="292"/>
+      <c r="H101" s="292"/>
+      <c r="I101" s="292"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="264" t="s">
+      <c r="A102" s="281" t="s">
         <v>349</v>
       </c>
-      <c r="B102" s="264"/>
-      <c r="D102" s="275"/>
-      <c r="E102" s="275"/>
-      <c r="F102" s="275"/>
-      <c r="G102" s="275"/>
-      <c r="H102" s="275"/>
-      <c r="I102" s="275"/>
+      <c r="B102" s="281"/>
+      <c r="D102" s="292"/>
+      <c r="E102" s="292"/>
+      <c r="F102" s="292"/>
+      <c r="G102" s="292"/>
+      <c r="H102" s="292"/>
+      <c r="I102" s="292"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="264"/>
-      <c r="B103" s="264"/>
-      <c r="D103" s="275"/>
-      <c r="E103" s="275"/>
-      <c r="F103" s="275"/>
-      <c r="G103" s="275"/>
-      <c r="H103" s="275"/>
-      <c r="I103" s="275"/>
+      <c r="A103" s="281"/>
+      <c r="B103" s="281"/>
+      <c r="D103" s="292"/>
+      <c r="E103" s="292"/>
+      <c r="F103" s="292"/>
+      <c r="G103" s="292"/>
+      <c r="H103" s="292"/>
+      <c r="I103" s="292"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="264"/>
-      <c r="B104" s="264"/>
-      <c r="D104" s="275"/>
-      <c r="E104" s="275"/>
-      <c r="F104" s="275"/>
-      <c r="G104" s="275"/>
-      <c r="H104" s="275"/>
-      <c r="I104" s="275"/>
+      <c r="A104" s="281"/>
+      <c r="B104" s="281"/>
+      <c r="D104" s="292"/>
+      <c r="E104" s="292"/>
+      <c r="F104" s="292"/>
+      <c r="G104" s="292"/>
+      <c r="H104" s="292"/>
+      <c r="I104" s="292"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="264"/>
-      <c r="B105" s="264"/>
-      <c r="D105" s="275"/>
-      <c r="E105" s="275"/>
-      <c r="F105" s="275"/>
-      <c r="G105" s="275"/>
-      <c r="H105" s="275"/>
-      <c r="I105" s="275"/>
+      <c r="A105" s="281"/>
+      <c r="B105" s="281"/>
+      <c r="D105" s="292"/>
+      <c r="E105" s="292"/>
+      <c r="F105" s="292"/>
+      <c r="G105" s="292"/>
+      <c r="H105" s="292"/>
+      <c r="I105" s="292"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="264"/>
-      <c r="B106" s="264"/>
-      <c r="D106" s="275"/>
-      <c r="E106" s="275"/>
-      <c r="F106" s="275"/>
-      <c r="G106" s="275"/>
-      <c r="H106" s="275"/>
-      <c r="I106" s="275"/>
+      <c r="A106" s="281"/>
+      <c r="B106" s="281"/>
+      <c r="D106" s="292"/>
+      <c r="E106" s="292"/>
+      <c r="F106" s="292"/>
+      <c r="G106" s="292"/>
+      <c r="H106" s="292"/>
+      <c r="I106" s="292"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="264"/>
-      <c r="B107" s="264"/>
-      <c r="D107" s="275"/>
-      <c r="E107" s="275"/>
-      <c r="F107" s="275"/>
-      <c r="G107" s="275"/>
-      <c r="H107" s="275"/>
-      <c r="I107" s="275"/>
+      <c r="A107" s="281"/>
+      <c r="B107" s="281"/>
+      <c r="D107" s="292"/>
+      <c r="E107" s="292"/>
+      <c r="F107" s="292"/>
+      <c r="G107" s="292"/>
+      <c r="H107" s="292"/>
+      <c r="I107" s="292"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D108" s="275"/>
-      <c r="E108" s="275"/>
-      <c r="F108" s="275"/>
-      <c r="G108" s="275"/>
-      <c r="H108" s="275"/>
-      <c r="I108" s="275"/>
+      <c r="D108" s="292"/>
+      <c r="E108" s="292"/>
+      <c r="F108" s="292"/>
+      <c r="G108" s="292"/>
+      <c r="H108" s="292"/>
+      <c r="I108" s="292"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="16" t="s">
@@ -5136,12 +5180,12 @@
       </c>
       <c r="B109" s="17"/>
       <c r="C109" s="18"/>
-      <c r="D109" s="275"/>
-      <c r="E109" s="275"/>
-      <c r="F109" s="275"/>
-      <c r="G109" s="275"/>
-      <c r="H109" s="275"/>
-      <c r="I109" s="275"/>
+      <c r="D109" s="292"/>
+      <c r="E109" s="292"/>
+      <c r="F109" s="292"/>
+      <c r="G109" s="292"/>
+      <c r="H109" s="292"/>
+      <c r="I109" s="292"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="19" t="s">
@@ -5151,12 +5195,12 @@
         <v>1499395.7189351022</v>
       </c>
       <c r="C110" s="20"/>
-      <c r="D110" s="275"/>
-      <c r="E110" s="275"/>
-      <c r="F110" s="275"/>
-      <c r="G110" s="275"/>
-      <c r="H110" s="275"/>
-      <c r="I110" s="275"/>
+      <c r="D110" s="292"/>
+      <c r="E110" s="292"/>
+      <c r="F110" s="292"/>
+      <c r="G110" s="292"/>
+      <c r="H110" s="292"/>
+      <c r="I110" s="292"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="21" t="s">
@@ -5169,12 +5213,12 @@
       <c r="C111" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D111" s="275"/>
-      <c r="E111" s="275"/>
-      <c r="F111" s="275"/>
-      <c r="G111" s="275"/>
-      <c r="H111" s="275"/>
-      <c r="I111" s="275"/>
+      <c r="D111" s="292"/>
+      <c r="E111" s="292"/>
+      <c r="F111" s="292"/>
+      <c r="G111" s="292"/>
+      <c r="H111" s="292"/>
+      <c r="I111" s="292"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="21" t="s">
@@ -5185,12 +5229,12 @@
         <v>7428990.9099999992</v>
       </c>
       <c r="C112" s="20"/>
-      <c r="D112" s="275"/>
-      <c r="E112" s="275"/>
-      <c r="F112" s="275"/>
-      <c r="G112" s="275"/>
-      <c r="H112" s="275"/>
-      <c r="I112" s="275"/>
+      <c r="D112" s="292"/>
+      <c r="E112" s="292"/>
+      <c r="F112" s="292"/>
+      <c r="G112" s="292"/>
+      <c r="H112" s="292"/>
+      <c r="I112" s="292"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="21" t="s">
@@ -5201,12 +5245,12 @@
         <v>-12414431.279999999</v>
       </c>
       <c r="C113" s="18"/>
-      <c r="D113" s="275"/>
-      <c r="E113" s="275"/>
-      <c r="F113" s="275"/>
-      <c r="G113" s="275"/>
-      <c r="H113" s="275"/>
-      <c r="I113" s="275"/>
+      <c r="D113" s="292"/>
+      <c r="E113" s="292"/>
+      <c r="F113" s="292"/>
+      <c r="G113" s="292"/>
+      <c r="H113" s="292"/>
+      <c r="I113" s="292"/>
       <c r="K113" s="44"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
@@ -5218,12 +5262,12 @@
         <v>0</v>
       </c>
       <c r="C114" s="18"/>
-      <c r="D114" s="275"/>
-      <c r="E114" s="275"/>
-      <c r="F114" s="275"/>
-      <c r="G114" s="275"/>
-      <c r="H114" s="275"/>
-      <c r="I114" s="275"/>
+      <c r="D114" s="292"/>
+      <c r="E114" s="292"/>
+      <c r="F114" s="292"/>
+      <c r="G114" s="292"/>
+      <c r="H114" s="292"/>
+      <c r="I114" s="292"/>
       <c r="K114" s="52"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
@@ -5235,12 +5279,12 @@
         <v>818000</v>
       </c>
       <c r="C115" s="18"/>
-      <c r="D115" s="275"/>
-      <c r="E115" s="275"/>
-      <c r="F115" s="275"/>
-      <c r="G115" s="275"/>
-      <c r="H115" s="275"/>
-      <c r="I115" s="275"/>
+      <c r="D115" s="292"/>
+      <c r="E115" s="292"/>
+      <c r="F115" s="292"/>
+      <c r="G115" s="292"/>
+      <c r="H115" s="292"/>
+      <c r="I115" s="292"/>
       <c r="K115" s="52"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
@@ -5252,12 +5296,12 @@
         <v>0</v>
       </c>
       <c r="C116" s="22"/>
-      <c r="D116" s="275"/>
-      <c r="E116" s="275"/>
-      <c r="F116" s="275"/>
-      <c r="G116" s="275"/>
-      <c r="H116" s="275"/>
-      <c r="I116" s="275"/>
+      <c r="D116" s="292"/>
+      <c r="E116" s="292"/>
+      <c r="F116" s="292"/>
+      <c r="G116" s="292"/>
+      <c r="H116" s="292"/>
+      <c r="I116" s="292"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="21" t="s">
@@ -5268,12 +5312,12 @@
         <v>0</v>
       </c>
       <c r="C117" s="22"/>
-      <c r="D117" s="275"/>
-      <c r="E117" s="275"/>
-      <c r="F117" s="275"/>
-      <c r="G117" s="275"/>
-      <c r="H117" s="275"/>
-      <c r="I117" s="275"/>
+      <c r="D117" s="292"/>
+      <c r="E117" s="292"/>
+      <c r="F117" s="292"/>
+      <c r="G117" s="292"/>
+      <c r="H117" s="292"/>
+      <c r="I117" s="292"/>
     </row>
     <row r="118" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="246" t="s">
@@ -5284,12 +5328,12 @@
         <v>-304977</v>
       </c>
       <c r="C118" s="22"/>
-      <c r="D118" s="275"/>
-      <c r="E118" s="275"/>
-      <c r="F118" s="275"/>
-      <c r="G118" s="275"/>
-      <c r="H118" s="275"/>
-      <c r="I118" s="275"/>
+      <c r="D118" s="292"/>
+      <c r="E118" s="292"/>
+      <c r="F118" s="292"/>
+      <c r="G118" s="292"/>
+      <c r="H118" s="292"/>
+      <c r="I118" s="292"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="19" t="s">
@@ -5300,22 +5344,22 @@
         <v>12236086.148935104</v>
       </c>
       <c r="C119" s="70"/>
-      <c r="D119" s="275"/>
-      <c r="E119" s="275"/>
-      <c r="F119" s="275"/>
-      <c r="G119" s="275"/>
-      <c r="H119" s="275"/>
-      <c r="I119" s="275"/>
+      <c r="D119" s="292"/>
+      <c r="E119" s="292"/>
+      <c r="F119" s="292"/>
+      <c r="G119" s="292"/>
+      <c r="H119" s="292"/>
+      <c r="I119" s="292"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="22"/>
       <c r="C120" s="18"/>
-      <c r="D120" s="275"/>
-      <c r="E120" s="275"/>
-      <c r="F120" s="275"/>
-      <c r="G120" s="275"/>
-      <c r="H120" s="275"/>
-      <c r="I120" s="275"/>
+      <c r="D120" s="292"/>
+      <c r="E120" s="292"/>
+      <c r="F120" s="292"/>
+      <c r="G120" s="292"/>
+      <c r="H120" s="292"/>
+      <c r="I120" s="292"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="16" t="s">
@@ -5323,12 +5367,12 @@
       </c>
       <c r="B121" s="8"/>
       <c r="C121" s="18"/>
-      <c r="D121" s="275"/>
-      <c r="E121" s="275"/>
-      <c r="F121" s="275"/>
-      <c r="G121" s="275"/>
-      <c r="H121" s="275"/>
-      <c r="I121" s="275"/>
+      <c r="D121" s="292"/>
+      <c r="E121" s="292"/>
+      <c r="F121" s="292"/>
+      <c r="G121" s="292"/>
+      <c r="H121" s="292"/>
+      <c r="I121" s="292"/>
     </row>
     <row r="122" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="19" t="s">
@@ -5445,50 +5489,50 @@
       <c r="R135" s="9"/>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B138" s="266"/>
-      <c r="C138" s="266"/>
-      <c r="D138" s="266"/>
-      <c r="E138" s="266"/>
+      <c r="B138" s="283"/>
+      <c r="C138" s="283"/>
+      <c r="D138" s="283"/>
+      <c r="E138" s="283"/>
       <c r="F138" s="90"/>
       <c r="G138" s="90"/>
       <c r="H138" s="90"/>
       <c r="I138" s="90"/>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B139" s="266"/>
-      <c r="C139" s="266"/>
-      <c r="D139" s="266"/>
-      <c r="E139" s="266"/>
+      <c r="B139" s="283"/>
+      <c r="C139" s="283"/>
+      <c r="D139" s="283"/>
+      <c r="E139" s="283"/>
       <c r="F139" s="90"/>
       <c r="G139" s="90"/>
       <c r="H139" s="90"/>
       <c r="I139" s="90"/>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B140" s="266"/>
-      <c r="C140" s="266"/>
-      <c r="D140" s="266"/>
-      <c r="E140" s="266"/>
+      <c r="B140" s="283"/>
+      <c r="C140" s="283"/>
+      <c r="D140" s="283"/>
+      <c r="E140" s="283"/>
       <c r="F140" s="90"/>
       <c r="G140" s="90"/>
       <c r="H140" s="90"/>
       <c r="I140" s="90"/>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B141" s="266"/>
-      <c r="C141" s="266"/>
-      <c r="D141" s="266"/>
-      <c r="E141" s="266"/>
+      <c r="B141" s="283"/>
+      <c r="C141" s="283"/>
+      <c r="D141" s="283"/>
+      <c r="E141" s="283"/>
       <c r="F141" s="90"/>
       <c r="G141" s="90"/>
       <c r="H141" s="90"/>
       <c r="I141" s="90"/>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B142" s="266"/>
-      <c r="C142" s="266"/>
-      <c r="D142" s="266"/>
-      <c r="E142" s="266"/>
+      <c r="B142" s="283"/>
+      <c r="C142" s="283"/>
+      <c r="D142" s="283"/>
+      <c r="E142" s="283"/>
       <c r="F142" s="90"/>
       <c r="G142" s="90"/>
       <c r="H142" s="90"/>
@@ -5545,13 +5589,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="312" t="s">
+      <c r="A1" s="325" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="313"/>
-      <c r="C1" s="313"/>
-      <c r="D1" s="313"/>
-      <c r="E1" s="313"/>
+      <c r="B1" s="326"/>
+      <c r="C1" s="326"/>
+      <c r="D1" s="326"/>
+      <c r="E1" s="326"/>
       <c r="F1" s="158" t="s">
         <v>285</v>
       </c>
@@ -5563,20 +5607,20 @@
       <c r="L1" s="189" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="291">
+      <c r="M1" s="301">
         <f>RESUMEN!D85-RESUMEN!D83</f>
         <v>12414431.279999999</v>
       </c>
-      <c r="N1" s="292"/>
+      <c r="N1" s="302"/>
       <c r="O1" s="159"/>
       <c r="P1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="314"/>
-      <c r="B2" s="315"/>
-      <c r="C2" s="315"/>
-      <c r="D2" s="315"/>
-      <c r="E2" s="315"/>
+      <c r="A2" s="327"/>
+      <c r="B2" s="328"/>
+      <c r="C2" s="328"/>
+      <c r="D2" s="328"/>
+      <c r="E2" s="328"/>
       <c r="F2" s="7" t="s">
         <v>284</v>
       </c>
@@ -5596,11 +5640,11 @@
       <c r="P2" s="59"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="314"/>
-      <c r="B3" s="315"/>
-      <c r="C3" s="315"/>
-      <c r="D3" s="315"/>
-      <c r="E3" s="315"/>
+      <c r="A3" s="327"/>
+      <c r="B3" s="328"/>
+      <c r="C3" s="328"/>
+      <c r="D3" s="328"/>
+      <c r="E3" s="328"/>
       <c r="F3" s="7" t="s">
         <v>286</v>
       </c>
@@ -5616,11 +5660,11 @@
       <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="316"/>
-      <c r="B4" s="317"/>
-      <c r="C4" s="317"/>
-      <c r="D4" s="317"/>
-      <c r="E4" s="317"/>
+      <c r="A4" s="329"/>
+      <c r="B4" s="330"/>
+      <c r="C4" s="330"/>
+      <c r="D4" s="330"/>
+      <c r="E4" s="330"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
       <c r="H4" s="163"/>
@@ -5636,95 +5680,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="297" t="s">
+      <c r="C5" s="310" t="s">
         <v>300</v>
       </c>
-      <c r="D5" s="298"/>
-      <c r="E5" s="298"/>
-      <c r="F5" s="298"/>
-      <c r="G5" s="298"/>
-      <c r="H5" s="298"/>
-      <c r="I5" s="298"/>
-      <c r="J5" s="298"/>
-      <c r="K5" s="298"/>
-      <c r="L5" s="298"/>
-      <c r="M5" s="298"/>
-      <c r="N5" s="298"/>
-      <c r="O5" s="299"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="311"/>
+      <c r="F5" s="311"/>
+      <c r="G5" s="311"/>
+      <c r="H5" s="311"/>
+      <c r="I5" s="311"/>
+      <c r="J5" s="311"/>
+      <c r="K5" s="311"/>
+      <c r="L5" s="311"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
+      <c r="O5" s="312"/>
       <c r="P5" s="15"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="300"/>
-      <c r="D6" s="301"/>
-      <c r="E6" s="301"/>
-      <c r="F6" s="301"/>
-      <c r="G6" s="301"/>
-      <c r="H6" s="301"/>
-      <c r="I6" s="301"/>
-      <c r="J6" s="301"/>
-      <c r="K6" s="301"/>
-      <c r="L6" s="301"/>
-      <c r="M6" s="301"/>
-      <c r="N6" s="301"/>
-      <c r="O6" s="302"/>
+      <c r="C6" s="313"/>
+      <c r="D6" s="314"/>
+      <c r="E6" s="314"/>
+      <c r="F6" s="314"/>
+      <c r="G6" s="314"/>
+      <c r="H6" s="314"/>
+      <c r="I6" s="314"/>
+      <c r="J6" s="314"/>
+      <c r="K6" s="314"/>
+      <c r="L6" s="314"/>
+      <c r="M6" s="314"/>
+      <c r="N6" s="314"/>
+      <c r="O6" s="315"/>
       <c r="P6" s="15"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="300"/>
-      <c r="D7" s="301"/>
-      <c r="E7" s="301"/>
-      <c r="F7" s="301"/>
-      <c r="G7" s="301"/>
-      <c r="H7" s="301"/>
-      <c r="I7" s="301"/>
-      <c r="J7" s="301"/>
-      <c r="K7" s="301"/>
-      <c r="L7" s="301"/>
-      <c r="M7" s="301"/>
-      <c r="N7" s="301"/>
-      <c r="O7" s="302"/>
+      <c r="C7" s="313"/>
+      <c r="D7" s="314"/>
+      <c r="E7" s="314"/>
+      <c r="F7" s="314"/>
+      <c r="G7" s="314"/>
+      <c r="H7" s="314"/>
+      <c r="I7" s="314"/>
+      <c r="J7" s="314"/>
+      <c r="K7" s="314"/>
+      <c r="L7" s="314"/>
+      <c r="M7" s="314"/>
+      <c r="N7" s="314"/>
+      <c r="O7" s="315"/>
       <c r="P7" s="15"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="303"/>
-      <c r="D8" s="304"/>
-      <c r="E8" s="304"/>
-      <c r="F8" s="304"/>
-      <c r="G8" s="304"/>
-      <c r="H8" s="304"/>
-      <c r="I8" s="304"/>
-      <c r="J8" s="304"/>
-      <c r="K8" s="304"/>
-      <c r="L8" s="304"/>
-      <c r="M8" s="304"/>
-      <c r="N8" s="304"/>
-      <c r="O8" s="305"/>
+      <c r="C8" s="316"/>
+      <c r="D8" s="317"/>
+      <c r="E8" s="317"/>
+      <c r="F8" s="317"/>
+      <c r="G8" s="317"/>
+      <c r="H8" s="317"/>
+      <c r="I8" s="317"/>
+      <c r="J8" s="317"/>
+      <c r="K8" s="317"/>
+      <c r="L8" s="317"/>
+      <c r="M8" s="317"/>
+      <c r="N8" s="317"/>
+      <c r="O8" s="318"/>
       <c r="Q8" s="84"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="306" t="s">
+      <c r="C9" s="319" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="307"/>
-      <c r="E9" s="307"/>
-      <c r="F9" s="307"/>
-      <c r="G9" s="307"/>
-      <c r="H9" s="307"/>
-      <c r="I9" s="307"/>
-      <c r="J9" s="307"/>
-      <c r="K9" s="307"/>
-      <c r="L9" s="307"/>
-      <c r="M9" s="307"/>
-      <c r="N9" s="307"/>
-      <c r="O9" s="308"/>
+      <c r="D9" s="320"/>
+      <c r="E9" s="320"/>
+      <c r="F9" s="320"/>
+      <c r="G9" s="320"/>
+      <c r="H9" s="320"/>
+      <c r="I9" s="320"/>
+      <c r="J9" s="320"/>
+      <c r="K9" s="320"/>
+      <c r="L9" s="320"/>
+      <c r="M9" s="320"/>
+      <c r="N9" s="320"/>
+      <c r="O9" s="321"/>
       <c r="Q9" t="s">
         <v>242</v>
       </c>
@@ -5736,19 +5780,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="309"/>
-      <c r="D10" s="310"/>
-      <c r="E10" s="310"/>
-      <c r="F10" s="310"/>
-      <c r="G10" s="310"/>
-      <c r="H10" s="310"/>
-      <c r="I10" s="310"/>
-      <c r="J10" s="310"/>
-      <c r="K10" s="310"/>
-      <c r="L10" s="310"/>
-      <c r="M10" s="310"/>
-      <c r="N10" s="310"/>
-      <c r="O10" s="311"/>
+      <c r="C10" s="322"/>
+      <c r="D10" s="323"/>
+      <c r="E10" s="323"/>
+      <c r="F10" s="323"/>
+      <c r="G10" s="323"/>
+      <c r="H10" s="323"/>
+      <c r="I10" s="323"/>
+      <c r="J10" s="323"/>
+      <c r="K10" s="323"/>
+      <c r="L10" s="323"/>
+      <c r="M10" s="323"/>
+      <c r="N10" s="323"/>
+      <c r="O10" s="324"/>
       <c r="Q10" t="s">
         <v>243</v>
       </c>
@@ -5758,49 +5802,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="282" t="s">
+      <c r="A11" s="297" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="284" t="s">
+      <c r="B11" s="331" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="282" t="s">
+      <c r="C11" s="297" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="286" t="s">
+      <c r="D11" s="333" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="286" t="s">
+      <c r="E11" s="333" t="s">
         <v>259</v>
       </c>
-      <c r="F11" s="282" t="s">
+      <c r="F11" s="297" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="282" t="s">
+      <c r="G11" s="297" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="282" t="s">
+      <c r="H11" s="297" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="293" t="s">
+      <c r="I11" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="279" t="s">
+      <c r="J11" s="305" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="279" t="s">
+      <c r="K11" s="305" t="s">
         <v>389</v>
       </c>
-      <c r="L11" s="279" t="s">
+      <c r="L11" s="305" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="295" t="s">
+      <c r="M11" s="308" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="279" t="s">
+      <c r="N11" s="305" t="s">
         <v>270</v>
       </c>
-      <c r="O11" s="279" t="s">
+      <c r="O11" s="305" t="s">
         <v>269</v>
       </c>
       <c r="Q11" t="s">
@@ -5812,21 +5856,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="283"/>
-      <c r="B12" s="285"/>
-      <c r="C12" s="283"/>
-      <c r="D12" s="287"/>
-      <c r="E12" s="287"/>
-      <c r="F12" s="283"/>
-      <c r="G12" s="283"/>
-      <c r="H12" s="283"/>
-      <c r="I12" s="294"/>
-      <c r="J12" s="280"/>
-      <c r="K12" s="280"/>
-      <c r="L12" s="280"/>
-      <c r="M12" s="296"/>
-      <c r="N12" s="280"/>
-      <c r="O12" s="280"/>
+      <c r="A12" s="298"/>
+      <c r="B12" s="332"/>
+      <c r="C12" s="298"/>
+      <c r="D12" s="334"/>
+      <c r="E12" s="334"/>
+      <c r="F12" s="298"/>
+      <c r="G12" s="298"/>
+      <c r="H12" s="298"/>
+      <c r="I12" s="304"/>
+      <c r="J12" s="306"/>
+      <c r="K12" s="306"/>
+      <c r="L12" s="306"/>
+      <c r="M12" s="309"/>
+      <c r="N12" s="306"/>
+      <c r="O12" s="306"/>
       <c r="Q12" t="s">
         <v>245</v>
       </c>
@@ -5836,19 +5880,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="283"/>
-      <c r="B13" s="285"/>
-      <c r="C13" s="283"/>
-      <c r="D13" s="287"/>
-      <c r="E13" s="287"/>
-      <c r="F13" s="283"/>
-      <c r="G13" s="283"/>
-      <c r="H13" s="283"/>
-      <c r="I13" s="294"/>
-      <c r="J13" s="280"/>
-      <c r="K13" s="281"/>
-      <c r="L13" s="281"/>
-      <c r="M13" s="296"/>
+      <c r="A13" s="298"/>
+      <c r="B13" s="332"/>
+      <c r="C13" s="298"/>
+      <c r="D13" s="334"/>
+      <c r="E13" s="334"/>
+      <c r="F13" s="298"/>
+      <c r="G13" s="298"/>
+      <c r="H13" s="298"/>
+      <c r="I13" s="304"/>
+      <c r="J13" s="306"/>
+      <c r="K13" s="307"/>
+      <c r="L13" s="307"/>
+      <c r="M13" s="309"/>
       <c r="N13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/04</v>
@@ -5866,14 +5910,14 @@
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="344" t="s">
+      <c r="A14" s="269" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="344"/>
-      <c r="C14" s="344" t="s">
+      <c r="B14" s="269"/>
+      <c r="C14" s="269" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="345" t="s">
+      <c r="D14" s="270" t="s">
         <v>175</v>
       </c>
       <c r="E14" s="108" t="s">
@@ -5917,16 +5961,16 @@
       <c r="P14" s="115" t="s">
         <v>384</v>
       </c>
-      <c r="R14" s="288"/>
-      <c r="S14" s="288"/>
+      <c r="R14" s="296"/>
+      <c r="S14" s="296"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="271" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="108" t="s">
+      <c r="D15" s="272" t="s">
         <v>310</v>
       </c>
       <c r="E15" s="188"/>
@@ -5967,8 +6011,8 @@
       <c r="P15" s="115" t="s">
         <v>381</v>
       </c>
-      <c r="R15" s="288"/>
-      <c r="S15" s="288"/>
+      <c r="R15" s="296"/>
+      <c r="S15" s="296"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -6344,10 +6388,10 @@
         <v>122</v>
       </c>
       <c r="B23" s="6"/>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="361" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="108" t="s">
+      <c r="D23" s="362" t="s">
         <v>181</v>
       </c>
       <c r="E23" s="135" t="s">
@@ -12643,34 +12687,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="290"/>
-      <c r="D135" s="290"/>
-      <c r="E135" s="290"/>
-      <c r="F135" s="290"/>
-      <c r="G135" s="290"/>
-      <c r="H135" s="290"/>
-      <c r="I135" s="290"/>
-      <c r="J135" s="290"/>
-      <c r="K135" s="290"/>
-      <c r="L135" s="290"/>
-      <c r="M135" s="290"/>
-      <c r="N135" s="290"/>
-      <c r="O135" s="290"/>
+      <c r="C135" s="300"/>
+      <c r="D135" s="300"/>
+      <c r="E135" s="300"/>
+      <c r="F135" s="300"/>
+      <c r="G135" s="300"/>
+      <c r="H135" s="300"/>
+      <c r="I135" s="300"/>
+      <c r="J135" s="300"/>
+      <c r="K135" s="300"/>
+      <c r="L135" s="300"/>
+      <c r="M135" s="300"/>
+      <c r="N135" s="300"/>
+      <c r="O135" s="300"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="290"/>
-      <c r="D136" s="290"/>
-      <c r="E136" s="290"/>
-      <c r="F136" s="290"/>
-      <c r="G136" s="290"/>
-      <c r="H136" s="290"/>
-      <c r="I136" s="290"/>
-      <c r="J136" s="290"/>
-      <c r="K136" s="290"/>
-      <c r="L136" s="290"/>
-      <c r="M136" s="290"/>
-      <c r="N136" s="290"/>
-      <c r="O136" s="290"/>
+      <c r="C136" s="300"/>
+      <c r="D136" s="300"/>
+      <c r="E136" s="300"/>
+      <c r="F136" s="300"/>
+      <c r="G136" s="300"/>
+      <c r="H136" s="300"/>
+      <c r="I136" s="300"/>
+      <c r="J136" s="300"/>
+      <c r="K136" s="300"/>
+      <c r="L136" s="300"/>
+      <c r="M136" s="300"/>
+      <c r="N136" s="300"/>
+      <c r="O136" s="300"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
@@ -12688,126 +12732,126 @@
       <c r="O137" s="77"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C138" s="264" t="s">
+      <c r="C138" s="281" t="s">
         <v>252</v>
       </c>
-      <c r="D138" s="264"/>
-      <c r="E138" s="264"/>
-      <c r="F138" s="264"/>
-      <c r="G138" s="264"/>
-      <c r="H138" s="264"/>
-      <c r="I138" s="264"/>
-      <c r="J138" s="264"/>
-      <c r="K138" s="264"/>
-      <c r="L138" s="264"/>
-      <c r="M138" s="264"/>
-      <c r="N138" s="264"/>
-      <c r="O138" s="264"/>
+      <c r="D138" s="281"/>
+      <c r="E138" s="281"/>
+      <c r="F138" s="281"/>
+      <c r="G138" s="281"/>
+      <c r="H138" s="281"/>
+      <c r="I138" s="281"/>
+      <c r="J138" s="281"/>
+      <c r="K138" s="281"/>
+      <c r="L138" s="281"/>
+      <c r="M138" s="281"/>
+      <c r="N138" s="281"/>
+      <c r="O138" s="281"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C139" s="264"/>
-      <c r="D139" s="264"/>
-      <c r="E139" s="264"/>
-      <c r="F139" s="264"/>
-      <c r="G139" s="264"/>
-      <c r="H139" s="264"/>
-      <c r="I139" s="264"/>
-      <c r="J139" s="264"/>
-      <c r="K139" s="264"/>
-      <c r="L139" s="264"/>
-      <c r="M139" s="264"/>
-      <c r="N139" s="264"/>
-      <c r="O139" s="264"/>
+      <c r="C139" s="281"/>
+      <c r="D139" s="281"/>
+      <c r="E139" s="281"/>
+      <c r="F139" s="281"/>
+      <c r="G139" s="281"/>
+      <c r="H139" s="281"/>
+      <c r="I139" s="281"/>
+      <c r="J139" s="281"/>
+      <c r="K139" s="281"/>
+      <c r="L139" s="281"/>
+      <c r="M139" s="281"/>
+      <c r="N139" s="281"/>
+      <c r="O139" s="281"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C140" s="264"/>
-      <c r="D140" s="264"/>
-      <c r="E140" s="264"/>
-      <c r="F140" s="264"/>
-      <c r="G140" s="264"/>
-      <c r="H140" s="264"/>
-      <c r="I140" s="264"/>
-      <c r="J140" s="264"/>
-      <c r="K140" s="264"/>
-      <c r="L140" s="264"/>
-      <c r="M140" s="264"/>
-      <c r="N140" s="264"/>
-      <c r="O140" s="264"/>
+      <c r="C140" s="281"/>
+      <c r="D140" s="281"/>
+      <c r="E140" s="281"/>
+      <c r="F140" s="281"/>
+      <c r="G140" s="281"/>
+      <c r="H140" s="281"/>
+      <c r="I140" s="281"/>
+      <c r="J140" s="281"/>
+      <c r="K140" s="281"/>
+      <c r="L140" s="281"/>
+      <c r="M140" s="281"/>
+      <c r="N140" s="281"/>
+      <c r="O140" s="281"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="264"/>
-      <c r="D141" s="264"/>
-      <c r="E141" s="264"/>
-      <c r="F141" s="264"/>
-      <c r="G141" s="264"/>
-      <c r="H141" s="264"/>
-      <c r="I141" s="264"/>
-      <c r="J141" s="264"/>
-      <c r="K141" s="264"/>
-      <c r="L141" s="264"/>
-      <c r="M141" s="264"/>
-      <c r="N141" s="264"/>
-      <c r="O141" s="264"/>
+      <c r="C141" s="281"/>
+      <c r="D141" s="281"/>
+      <c r="E141" s="281"/>
+      <c r="F141" s="281"/>
+      <c r="G141" s="281"/>
+      <c r="H141" s="281"/>
+      <c r="I141" s="281"/>
+      <c r="J141" s="281"/>
+      <c r="K141" s="281"/>
+      <c r="L141" s="281"/>
+      <c r="M141" s="281"/>
+      <c r="N141" s="281"/>
+      <c r="O141" s="281"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C142" s="264"/>
-      <c r="D142" s="264"/>
-      <c r="E142" s="264"/>
-      <c r="F142" s="264"/>
-      <c r="G142" s="264"/>
-      <c r="H142" s="264"/>
-      <c r="I142" s="264"/>
-      <c r="J142" s="264"/>
-      <c r="K142" s="264"/>
-      <c r="L142" s="264"/>
-      <c r="M142" s="264"/>
-      <c r="N142" s="264"/>
-      <c r="O142" s="264"/>
+      <c r="C142" s="281"/>
+      <c r="D142" s="281"/>
+      <c r="E142" s="281"/>
+      <c r="F142" s="281"/>
+      <c r="G142" s="281"/>
+      <c r="H142" s="281"/>
+      <c r="I142" s="281"/>
+      <c r="J142" s="281"/>
+      <c r="K142" s="281"/>
+      <c r="L142" s="281"/>
+      <c r="M142" s="281"/>
+      <c r="N142" s="281"/>
+      <c r="O142" s="281"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C143" s="264"/>
-      <c r="D143" s="264"/>
-      <c r="E143" s="264"/>
-      <c r="F143" s="264"/>
-      <c r="G143" s="264"/>
-      <c r="H143" s="264"/>
-      <c r="I143" s="264"/>
-      <c r="J143" s="264"/>
-      <c r="K143" s="264"/>
-      <c r="L143" s="264"/>
-      <c r="M143" s="264"/>
-      <c r="N143" s="264"/>
-      <c r="O143" s="264"/>
+      <c r="C143" s="281"/>
+      <c r="D143" s="281"/>
+      <c r="E143" s="281"/>
+      <c r="F143" s="281"/>
+      <c r="G143" s="281"/>
+      <c r="H143" s="281"/>
+      <c r="I143" s="281"/>
+      <c r="J143" s="281"/>
+      <c r="K143" s="281"/>
+      <c r="L143" s="281"/>
+      <c r="M143" s="281"/>
+      <c r="N143" s="281"/>
+      <c r="O143" s="281"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C144" s="264"/>
-      <c r="D144" s="264"/>
-      <c r="E144" s="264"/>
-      <c r="F144" s="264"/>
-      <c r="G144" s="264"/>
-      <c r="H144" s="264"/>
-      <c r="I144" s="264"/>
-      <c r="J144" s="264"/>
-      <c r="K144" s="264"/>
-      <c r="L144" s="264"/>
-      <c r="M144" s="264"/>
-      <c r="N144" s="264"/>
-      <c r="O144" s="264"/>
+      <c r="C144" s="281"/>
+      <c r="D144" s="281"/>
+      <c r="E144" s="281"/>
+      <c r="F144" s="281"/>
+      <c r="G144" s="281"/>
+      <c r="H144" s="281"/>
+      <c r="I144" s="281"/>
+      <c r="J144" s="281"/>
+      <c r="K144" s="281"/>
+      <c r="L144" s="281"/>
+      <c r="M144" s="281"/>
+      <c r="N144" s="281"/>
+      <c r="O144" s="281"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C145" s="264"/>
-      <c r="D145" s="264"/>
-      <c r="E145" s="264"/>
-      <c r="F145" s="264"/>
-      <c r="G145" s="264"/>
-      <c r="H145" s="264"/>
-      <c r="I145" s="264"/>
-      <c r="J145" s="264"/>
-      <c r="K145" s="264"/>
-      <c r="L145" s="264"/>
-      <c r="M145" s="264"/>
-      <c r="N145" s="264"/>
-      <c r="O145" s="264"/>
+      <c r="C145" s="281"/>
+      <c r="D145" s="281"/>
+      <c r="E145" s="281"/>
+      <c r="F145" s="281"/>
+      <c r="G145" s="281"/>
+      <c r="H145" s="281"/>
+      <c r="I145" s="281"/>
+      <c r="J145" s="281"/>
+      <c r="K145" s="281"/>
+      <c r="L145" s="281"/>
+      <c r="M145" s="281"/>
+      <c r="N145" s="281"/>
+      <c r="O145" s="281"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="77"/>
@@ -12840,118 +12884,125 @@
       <c r="O147" s="77"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C148" s="289" t="s">
+      <c r="C148" s="299" t="s">
         <v>251</v>
       </c>
-      <c r="D148" s="289"/>
-      <c r="E148" s="289"/>
-      <c r="F148" s="289"/>
-      <c r="G148" s="289"/>
-      <c r="H148" s="289"/>
-      <c r="I148" s="289"/>
-      <c r="J148" s="289"/>
-      <c r="K148" s="289"/>
-      <c r="L148" s="289"/>
-      <c r="M148" s="289"/>
-      <c r="N148" s="289"/>
-      <c r="O148" s="289"/>
+      <c r="D148" s="299"/>
+      <c r="E148" s="299"/>
+      <c r="F148" s="299"/>
+      <c r="G148" s="299"/>
+      <c r="H148" s="299"/>
+      <c r="I148" s="299"/>
+      <c r="J148" s="299"/>
+      <c r="K148" s="299"/>
+      <c r="L148" s="299"/>
+      <c r="M148" s="299"/>
+      <c r="N148" s="299"/>
+      <c r="O148" s="299"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="289"/>
-      <c r="D149" s="289"/>
-      <c r="E149" s="289"/>
-      <c r="F149" s="289"/>
-      <c r="G149" s="289"/>
-      <c r="H149" s="289"/>
-      <c r="I149" s="289"/>
-      <c r="J149" s="289"/>
-      <c r="K149" s="289"/>
-      <c r="L149" s="289"/>
-      <c r="M149" s="289"/>
-      <c r="N149" s="289"/>
-      <c r="O149" s="289"/>
+      <c r="C149" s="299"/>
+      <c r="D149" s="299"/>
+      <c r="E149" s="299"/>
+      <c r="F149" s="299"/>
+      <c r="G149" s="299"/>
+      <c r="H149" s="299"/>
+      <c r="I149" s="299"/>
+      <c r="J149" s="299"/>
+      <c r="K149" s="299"/>
+      <c r="L149" s="299"/>
+      <c r="M149" s="299"/>
+      <c r="N149" s="299"/>
+      <c r="O149" s="299"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="289"/>
-      <c r="D150" s="289"/>
-      <c r="E150" s="289"/>
-      <c r="F150" s="289"/>
-      <c r="G150" s="289"/>
-      <c r="H150" s="289"/>
-      <c r="I150" s="289"/>
-      <c r="J150" s="289"/>
-      <c r="K150" s="289"/>
-      <c r="L150" s="289"/>
-      <c r="M150" s="289"/>
-      <c r="N150" s="289"/>
-      <c r="O150" s="289"/>
+      <c r="C150" s="299"/>
+      <c r="D150" s="299"/>
+      <c r="E150" s="299"/>
+      <c r="F150" s="299"/>
+      <c r="G150" s="299"/>
+      <c r="H150" s="299"/>
+      <c r="I150" s="299"/>
+      <c r="J150" s="299"/>
+      <c r="K150" s="299"/>
+      <c r="L150" s="299"/>
+      <c r="M150" s="299"/>
+      <c r="N150" s="299"/>
+      <c r="O150" s="299"/>
       <c r="Q150" s="84">
         <f>M1-L133</f>
         <v>467629.98223999888</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="289"/>
-      <c r="D151" s="289"/>
-      <c r="E151" s="289"/>
-      <c r="F151" s="289"/>
-      <c r="G151" s="289"/>
-      <c r="H151" s="289"/>
-      <c r="I151" s="289"/>
-      <c r="J151" s="289"/>
-      <c r="K151" s="289"/>
-      <c r="L151" s="289"/>
-      <c r="M151" s="289"/>
-      <c r="N151" s="289"/>
-      <c r="O151" s="289"/>
+      <c r="C151" s="299"/>
+      <c r="D151" s="299"/>
+      <c r="E151" s="299"/>
+      <c r="F151" s="299"/>
+      <c r="G151" s="299"/>
+      <c r="H151" s="299"/>
+      <c r="I151" s="299"/>
+      <c r="J151" s="299"/>
+      <c r="K151" s="299"/>
+      <c r="L151" s="299"/>
+      <c r="M151" s="299"/>
+      <c r="N151" s="299"/>
+      <c r="O151" s="299"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="289"/>
-      <c r="D152" s="289"/>
-      <c r="E152" s="289"/>
-      <c r="F152" s="289"/>
-      <c r="G152" s="289"/>
-      <c r="H152" s="289"/>
-      <c r="I152" s="289"/>
-      <c r="J152" s="289"/>
-      <c r="K152" s="289"/>
-      <c r="L152" s="289"/>
-      <c r="M152" s="289"/>
-      <c r="N152" s="289"/>
-      <c r="O152" s="289"/>
+      <c r="C152" s="299"/>
+      <c r="D152" s="299"/>
+      <c r="E152" s="299"/>
+      <c r="F152" s="299"/>
+      <c r="G152" s="299"/>
+      <c r="H152" s="299"/>
+      <c r="I152" s="299"/>
+      <c r="J152" s="299"/>
+      <c r="K152" s="299"/>
+      <c r="L152" s="299"/>
+      <c r="M152" s="299"/>
+      <c r="N152" s="299"/>
+      <c r="O152" s="299"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="289"/>
-      <c r="D153" s="289"/>
-      <c r="E153" s="289"/>
-      <c r="F153" s="289"/>
-      <c r="G153" s="289"/>
-      <c r="H153" s="289"/>
-      <c r="I153" s="289"/>
-      <c r="J153" s="289"/>
-      <c r="K153" s="289"/>
-      <c r="L153" s="289"/>
-      <c r="M153" s="289"/>
-      <c r="N153" s="289"/>
-      <c r="O153" s="289"/>
+      <c r="C153" s="299"/>
+      <c r="D153" s="299"/>
+      <c r="E153" s="299"/>
+      <c r="F153" s="299"/>
+      <c r="G153" s="299"/>
+      <c r="H153" s="299"/>
+      <c r="I153" s="299"/>
+      <c r="J153" s="299"/>
+      <c r="K153" s="299"/>
+      <c r="L153" s="299"/>
+      <c r="M153" s="299"/>
+      <c r="N153" s="299"/>
+      <c r="O153" s="299"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="289"/>
-      <c r="D154" s="289"/>
-      <c r="E154" s="289"/>
-      <c r="F154" s="289"/>
-      <c r="G154" s="289"/>
-      <c r="H154" s="289"/>
-      <c r="I154" s="289"/>
-      <c r="J154" s="289"/>
-      <c r="K154" s="289"/>
-      <c r="L154" s="289"/>
-      <c r="M154" s="289"/>
-      <c r="N154" s="289"/>
-      <c r="O154" s="289"/>
+      <c r="C154" s="299"/>
+      <c r="D154" s="299"/>
+      <c r="E154" s="299"/>
+      <c r="F154" s="299"/>
+      <c r="G154" s="299"/>
+      <c r="H154" s="299"/>
+      <c r="I154" s="299"/>
+      <c r="J154" s="299"/>
+      <c r="K154" s="299"/>
+      <c r="L154" s="299"/>
+      <c r="M154" s="299"/>
+      <c r="N154" s="299"/>
+      <c r="O154" s="299"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -12968,13 +13019,6 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13007,61 +13051,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="322" t="s">
+      <c r="A1" s="338" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="322"/>
-      <c r="C1" s="322"/>
-      <c r="D1" s="322"/>
-      <c r="E1" s="322"/>
-      <c r="F1" s="322"/>
-      <c r="G1" s="322"/>
-      <c r="H1" s="322"/>
-      <c r="I1" s="322"/>
-      <c r="J1" s="322"/>
-      <c r="K1" s="322"/>
-      <c r="L1" s="322"/>
-      <c r="M1" s="322"/>
-      <c r="N1" s="322"/>
-      <c r="O1" s="323"/>
+      <c r="B1" s="338"/>
+      <c r="C1" s="338"/>
+      <c r="D1" s="338"/>
+      <c r="E1" s="338"/>
+      <c r="F1" s="338"/>
+      <c r="G1" s="338"/>
+      <c r="H1" s="338"/>
+      <c r="I1" s="338"/>
+      <c r="J1" s="338"/>
+      <c r="K1" s="338"/>
+      <c r="L1" s="338"/>
+      <c r="M1" s="338"/>
+      <c r="N1" s="338"/>
+      <c r="O1" s="339"/>
       <c r="R1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="324"/>
-      <c r="B2" s="324"/>
-      <c r="C2" s="324"/>
-      <c r="D2" s="324"/>
-      <c r="E2" s="324"/>
-      <c r="F2" s="324"/>
-      <c r="G2" s="324"/>
-      <c r="H2" s="324"/>
-      <c r="I2" s="324"/>
-      <c r="J2" s="324"/>
-      <c r="K2" s="324"/>
-      <c r="L2" s="324"/>
-      <c r="M2" s="324"/>
-      <c r="N2" s="324"/>
-      <c r="O2" s="325"/>
+      <c r="A2" s="340"/>
+      <c r="B2" s="340"/>
+      <c r="C2" s="340"/>
+      <c r="D2" s="340"/>
+      <c r="E2" s="340"/>
+      <c r="F2" s="340"/>
+      <c r="G2" s="340"/>
+      <c r="H2" s="340"/>
+      <c r="I2" s="340"/>
+      <c r="J2" s="340"/>
+      <c r="K2" s="340"/>
+      <c r="L2" s="340"/>
+      <c r="M2" s="340"/>
+      <c r="N2" s="340"/>
+      <c r="O2" s="341"/>
       <c r="R2" s="43"/>
     </row>
     <row r="3" spans="1:27" s="240" customFormat="1" ht="299.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="319" t="s">
+      <c r="A3" s="335" t="s">
         <v>390</v>
       </c>
-      <c r="B3" s="320"/>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
-      <c r="I3" s="320"/>
-      <c r="J3" s="320"/>
-      <c r="K3" s="320"/>
-      <c r="L3" s="320"/>
-      <c r="M3" s="320"/>
-      <c r="N3" s="320"/>
-      <c r="O3" s="321"/>
+      <c r="B3" s="336"/>
+      <c r="C3" s="336"/>
+      <c r="D3" s="336"/>
+      <c r="E3" s="336"/>
+      <c r="F3" s="336"/>
+      <c r="G3" s="336"/>
+      <c r="H3" s="336"/>
+      <c r="I3" s="336"/>
+      <c r="J3" s="336"/>
+      <c r="K3" s="336"/>
+      <c r="L3" s="336"/>
+      <c r="M3" s="336"/>
+      <c r="N3" s="336"/>
+      <c r="O3" s="337"/>
       <c r="P3" s="241"/>
       <c r="Q3" s="241"/>
       <c r="R3" s="241"/>
@@ -13076,85 +13120,85 @@
       <c r="AA3" s="241"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="282" t="s">
+      <c r="A4" s="297" t="s">
         <v>315</v>
       </c>
-      <c r="B4" s="282" t="s">
+      <c r="B4" s="297" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="282" t="s">
+      <c r="C4" s="297" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="282" t="s">
+      <c r="D4" s="297" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="279" t="s">
+      <c r="E4" s="305" t="s">
         <v>342</v>
       </c>
-      <c r="F4" s="279" t="s">
+      <c r="F4" s="305" t="s">
         <v>343</v>
       </c>
-      <c r="G4" s="279" t="s">
+      <c r="G4" s="305" t="s">
         <v>270</v>
       </c>
-      <c r="H4" s="279" t="s">
+      <c r="H4" s="305" t="s">
         <v>350</v>
       </c>
-      <c r="I4" s="279" t="s">
+      <c r="I4" s="305" t="s">
         <v>379</v>
       </c>
-      <c r="J4" s="326" t="s">
+      <c r="J4" s="342" t="s">
         <v>344</v>
       </c>
       <c r="K4" s="131"/>
-      <c r="L4" s="279" t="s">
+      <c r="L4" s="305" t="s">
         <v>376</v>
       </c>
-      <c r="M4" s="279" t="s">
+      <c r="M4" s="305" t="s">
         <v>377</v>
       </c>
-      <c r="N4" s="279" t="s">
+      <c r="N4" s="305" t="s">
         <v>345</v>
       </c>
-      <c r="O4" s="279" t="s">
+      <c r="O4" s="305" t="s">
         <v>17</v>
       </c>
       <c r="R4" s="43"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="283"/>
-      <c r="B5" s="283"/>
-      <c r="C5" s="283"/>
-      <c r="D5" s="283"/>
-      <c r="E5" s="280"/>
-      <c r="F5" s="280"/>
-      <c r="G5" s="280"/>
-      <c r="H5" s="280"/>
-      <c r="I5" s="280"/>
-      <c r="J5" s="327"/>
+      <c r="A5" s="298"/>
+      <c r="B5" s="298"/>
+      <c r="C5" s="298"/>
+      <c r="D5" s="298"/>
+      <c r="E5" s="306"/>
+      <c r="F5" s="306"/>
+      <c r="G5" s="306"/>
+      <c r="H5" s="306"/>
+      <c r="I5" s="306"/>
+      <c r="J5" s="343"/>
       <c r="K5" s="131"/>
-      <c r="L5" s="280"/>
-      <c r="M5" s="280"/>
-      <c r="N5" s="280"/>
-      <c r="O5" s="280"/>
+      <c r="L5" s="306"/>
+      <c r="M5" s="306"/>
+      <c r="N5" s="306"/>
+      <c r="O5" s="306"/>
       <c r="R5" s="43"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="329"/>
-      <c r="B6" s="329"/>
-      <c r="C6" s="329"/>
-      <c r="D6" s="329"/>
-      <c r="E6" s="318"/>
-      <c r="F6" s="318"/>
-      <c r="G6" s="318"/>
-      <c r="H6" s="318"/>
-      <c r="I6" s="318"/>
-      <c r="J6" s="328"/>
+      <c r="A6" s="346"/>
+      <c r="B6" s="346"/>
+      <c r="C6" s="346"/>
+      <c r="D6" s="346"/>
+      <c r="E6" s="345"/>
+      <c r="F6" s="345"/>
+      <c r="G6" s="345"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="344"/>
       <c r="K6" s="205"/>
-      <c r="L6" s="318"/>
-      <c r="M6" s="318"/>
-      <c r="N6" s="318"/>
-      <c r="O6" s="318"/>
+      <c r="L6" s="345"/>
+      <c r="M6" s="345"/>
+      <c r="N6" s="345"/>
+      <c r="O6" s="345"/>
       <c r="R6" s="43"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
@@ -13211,8 +13255,8 @@
       <c r="P7" s="115">
         <v>0.7</v>
       </c>
-      <c r="R7" s="288"/>
-      <c r="S7" s="288"/>
+      <c r="R7" s="296"/>
+      <c r="S7" s="296"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="206" t="s">
@@ -13266,8 +13310,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="288"/>
-      <c r="S8" s="288"/>
+      <c r="R8" s="296"/>
+      <c r="S8" s="296"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="206" t="s">
@@ -17745,8 +17789,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
@@ -17762,6 +17804,8 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17770,7 +17814,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C2:J18"/>
+  <dimension ref="C2:J45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -17839,47 +17883,47 @@
       <c r="J6" s="261"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="330" t="s">
+      <c r="C7" s="347" t="s">
         <v>401</v>
       </c>
-      <c r="D7" s="331"/>
-      <c r="E7" s="331"/>
-      <c r="F7" s="331"/>
-      <c r="G7" s="331"/>
-      <c r="H7" s="331"/>
-      <c r="I7" s="331"/>
-      <c r="J7" s="332"/>
+      <c r="D7" s="348"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
+      <c r="G7" s="348"/>
+      <c r="H7" s="348"/>
+      <c r="I7" s="348"/>
+      <c r="J7" s="349"/>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="333"/>
-      <c r="D8" s="334"/>
-      <c r="E8" s="334"/>
-      <c r="F8" s="334"/>
-      <c r="G8" s="334"/>
-      <c r="H8" s="334"/>
-      <c r="I8" s="334"/>
-      <c r="J8" s="335"/>
+      <c r="C8" s="350"/>
+      <c r="D8" s="351"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
+      <c r="G8" s="351"/>
+      <c r="H8" s="351"/>
+      <c r="I8" s="351"/>
+      <c r="J8" s="352"/>
     </row>
     <row r="9" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="336"/>
-      <c r="D9" s="337"/>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
-      <c r="G9" s="337"/>
-      <c r="H9" s="337"/>
-      <c r="I9" s="337"/>
-      <c r="J9" s="338"/>
+      <c r="C9" s="353"/>
+      <c r="D9" s="354"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
+      <c r="G9" s="354"/>
+      <c r="H9" s="354"/>
+      <c r="I9" s="354"/>
+      <c r="J9" s="355"/>
     </row>
     <row r="11" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="339" t="s">
+      <c r="C12" s="264" t="s">
         <v>391</v>
       </c>
-      <c r="D12" s="340">
+      <c r="D12" s="265">
         <f>D3+1</f>
         <v>2</v>
       </c>
-      <c r="E12" s="340"/>
+      <c r="E12" s="265"/>
       <c r="F12" s="253"/>
       <c r="G12" s="253"/>
       <c r="H12" s="253"/>
@@ -17887,11 +17931,11 @@
       <c r="J12" s="254"/>
     </row>
     <row r="13" spans="3:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="341" t="s">
+      <c r="C13" s="266" t="s">
         <v>392</v>
       </c>
-      <c r="D13" s="342"/>
-      <c r="E13" s="343">
+      <c r="D13" s="267"/>
+      <c r="E13" s="268">
         <v>0</v>
       </c>
       <c r="F13" s="73"/>
@@ -17903,13 +17947,13 @@
       <c r="J13" s="260"/>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="341" t="s">
+      <c r="C14" s="266" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="342" t="s">
+      <c r="D14" s="267" t="s">
         <v>395</v>
       </c>
-      <c r="E14" s="342" t="s">
+      <c r="E14" s="267" t="s">
         <v>396</v>
       </c>
       <c r="F14" s="73"/>
@@ -17935,41 +17979,334 @@
       <c r="J15" s="261"/>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="330" t="s">
+      <c r="C16" s="347" t="s">
         <v>403</v>
       </c>
-      <c r="D16" s="331"/>
-      <c r="E16" s="331"/>
-      <c r="F16" s="331"/>
-      <c r="G16" s="331"/>
-      <c r="H16" s="331"/>
-      <c r="I16" s="331"/>
-      <c r="J16" s="332"/>
+      <c r="D16" s="348"/>
+      <c r="E16" s="348"/>
+      <c r="F16" s="348"/>
+      <c r="G16" s="348"/>
+      <c r="H16" s="348"/>
+      <c r="I16" s="348"/>
+      <c r="J16" s="349"/>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="333"/>
-      <c r="D17" s="334"/>
-      <c r="E17" s="334"/>
-      <c r="F17" s="334"/>
-      <c r="G17" s="334"/>
-      <c r="H17" s="334"/>
-      <c r="I17" s="334"/>
-      <c r="J17" s="335"/>
+      <c r="C17" s="350"/>
+      <c r="D17" s="351"/>
+      <c r="E17" s="351"/>
+      <c r="F17" s="351"/>
+      <c r="G17" s="351"/>
+      <c r="H17" s="351"/>
+      <c r="I17" s="351"/>
+      <c r="J17" s="352"/>
     </row>
     <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="336"/>
-      <c r="D18" s="337"/>
-      <c r="E18" s="337"/>
-      <c r="F18" s="337"/>
-      <c r="G18" s="337"/>
-      <c r="H18" s="337"/>
-      <c r="I18" s="337"/>
-      <c r="J18" s="338"/>
+      <c r="C18" s="353"/>
+      <c r="D18" s="354"/>
+      <c r="E18" s="354"/>
+      <c r="F18" s="354"/>
+      <c r="G18" s="354"/>
+      <c r="H18" s="354"/>
+      <c r="I18" s="354"/>
+      <c r="J18" s="355"/>
+    </row>
+    <row r="20" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="273" t="s">
+        <v>391</v>
+      </c>
+      <c r="D21" s="274">
+        <f>D12+1</f>
+        <v>3</v>
+      </c>
+      <c r="E21" s="274"/>
+      <c r="F21" s="253"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
+      <c r="I21" s="253"/>
+      <c r="J21" s="254"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="275" t="s">
+        <v>392</v>
+      </c>
+      <c r="D22" s="276"/>
+      <c r="E22" s="277">
+        <v>0</v>
+      </c>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73" t="s">
+        <v>393</v>
+      </c>
+      <c r="H22" s="258"/>
+      <c r="I22" s="259"/>
+      <c r="J22" s="260"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="275" t="s">
+        <v>394</v>
+      </c>
+      <c r="D23" s="276" t="s">
+        <v>395</v>
+      </c>
+      <c r="E23" s="276" t="s">
+        <v>396</v>
+      </c>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73" t="s">
+        <v>397</v>
+      </c>
+      <c r="H23" t="s">
+        <v>404</v>
+      </c>
+      <c r="I23" s="259"/>
+      <c r="J23" s="260"/>
+    </row>
+    <row r="24" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="244" t="s">
+        <v>398</v>
+      </c>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="261"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="347" t="s">
+        <v>405</v>
+      </c>
+      <c r="D25" s="348"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
+      <c r="G25" s="348"/>
+      <c r="H25" s="348"/>
+      <c r="I25" s="348"/>
+      <c r="J25" s="349"/>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="350"/>
+      <c r="D26" s="351"/>
+      <c r="E26" s="351"/>
+      <c r="F26" s="351"/>
+      <c r="G26" s="351"/>
+      <c r="H26" s="351"/>
+      <c r="I26" s="351"/>
+      <c r="J26" s="352"/>
+    </row>
+    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="353"/>
+      <c r="D27" s="354"/>
+      <c r="E27" s="354"/>
+      <c r="F27" s="354"/>
+      <c r="G27" s="354"/>
+      <c r="H27" s="354"/>
+      <c r="I27" s="354"/>
+      <c r="J27" s="355"/>
+    </row>
+    <row r="29" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="112" t="s">
+        <v>391</v>
+      </c>
+      <c r="D30" s="110">
+        <f>D21+1</f>
+        <v>4</v>
+      </c>
+      <c r="E30" s="110"/>
+      <c r="F30" s="253"/>
+      <c r="G30" s="253"/>
+      <c r="H30" s="253"/>
+      <c r="I30" s="253"/>
+      <c r="J30" s="254"/>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="278" t="s">
+        <v>392</v>
+      </c>
+      <c r="D31" s="279"/>
+      <c r="E31" s="280">
+        <v>0</v>
+      </c>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73" t="s">
+        <v>393</v>
+      </c>
+      <c r="H31" s="258" t="s">
+        <v>408</v>
+      </c>
+      <c r="I31" s="259"/>
+      <c r="J31" s="260"/>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="278" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" s="279" t="s">
+        <v>395</v>
+      </c>
+      <c r="E32" s="279" t="s">
+        <v>396</v>
+      </c>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73" t="s">
+        <v>397</v>
+      </c>
+      <c r="H32" t="s">
+        <v>407</v>
+      </c>
+      <c r="I32" s="259"/>
+      <c r="J32" s="260"/>
+    </row>
+    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="244" t="s">
+        <v>398</v>
+      </c>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="261"/>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C34" s="347" t="s">
+        <v>406</v>
+      </c>
+      <c r="D34" s="348"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
+      <c r="G34" s="348"/>
+      <c r="H34" s="348"/>
+      <c r="I34" s="348"/>
+      <c r="J34" s="349"/>
+    </row>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C35" s="350"/>
+      <c r="D35" s="351"/>
+      <c r="E35" s="351"/>
+      <c r="F35" s="351"/>
+      <c r="G35" s="351"/>
+      <c r="H35" s="351"/>
+      <c r="I35" s="351"/>
+      <c r="J35" s="352"/>
+    </row>
+    <row r="36" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C36" s="353"/>
+      <c r="D36" s="354"/>
+      <c r="E36" s="354"/>
+      <c r="F36" s="354"/>
+      <c r="G36" s="354"/>
+      <c r="H36" s="354"/>
+      <c r="I36" s="354"/>
+      <c r="J36" s="355"/>
+    </row>
+    <row r="38" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C39" s="356" t="s">
+        <v>391</v>
+      </c>
+      <c r="D39" s="357">
+        <f>D30+1</f>
+        <v>5</v>
+      </c>
+      <c r="E39" s="357"/>
+      <c r="F39" s="253"/>
+      <c r="G39" s="253"/>
+      <c r="H39" s="253"/>
+      <c r="I39" s="253"/>
+      <c r="J39" s="254"/>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C40" s="358" t="s">
+        <v>392</v>
+      </c>
+      <c r="D40" s="359"/>
+      <c r="E40" s="360">
+        <v>0</v>
+      </c>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73" t="s">
+        <v>393</v>
+      </c>
+      <c r="H40" s="258"/>
+      <c r="I40" s="259"/>
+      <c r="J40" s="260"/>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C41" s="358" t="s">
+        <v>394</v>
+      </c>
+      <c r="D41" s="359" t="s">
+        <v>395</v>
+      </c>
+      <c r="E41" s="359" t="s">
+        <v>396</v>
+      </c>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73" t="s">
+        <v>397</v>
+      </c>
+      <c r="H41" t="s">
+        <v>409</v>
+      </c>
+      <c r="I41" s="259"/>
+      <c r="J41" s="260"/>
+    </row>
+    <row r="42" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="244" t="s">
+        <v>398</v>
+      </c>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="261"/>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C43" s="347" t="s">
+        <v>410</v>
+      </c>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
+      <c r="G43" s="348"/>
+      <c r="H43" s="348"/>
+      <c r="I43" s="348"/>
+      <c r="J43" s="349"/>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C44" s="350"/>
+      <c r="D44" s="351"/>
+      <c r="E44" s="351"/>
+      <c r="F44" s="351"/>
+      <c r="G44" s="351"/>
+      <c r="H44" s="351"/>
+      <c r="I44" s="351"/>
+      <c r="J44" s="352"/>
+    </row>
+    <row r="45" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C45" s="353"/>
+      <c r="D45" s="354"/>
+      <c r="E45" s="354"/>
+      <c r="F45" s="354"/>
+      <c r="G45" s="354"/>
+      <c r="H45" s="354"/>
+      <c r="I45" s="354"/>
+      <c r="J45" s="355"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="C7:J9"/>
     <mergeCell ref="C16:J18"/>
+    <mergeCell ref="C25:J27"/>
+    <mergeCell ref="C34:J36"/>
+    <mergeCell ref="C43:J45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
